--- a/S-158-104/1.1.0/WD-158_104_1_1_0_20260915.xlsx
+++ b/S-158-104/1.1.0/WD-158_104_1_1_0_20260915.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\TWCWG\S-158-104\1.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2814ABD-BD8F-40C3-BED5-F48CFDF80DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF0E0EB-53E4-420E-97E0-9647686F96E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S-104'!$B$1:$B$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S-104'!$B$1:$B$444</definedName>
     <definedName name="S101_Disposition">[1]Lists!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="600">
   <si>
     <t>Classification</t>
   </si>
@@ -1911,24 +1911,6 @@
     <t>Definition (from S-100 Table 10c-10)</t>
   </si>
   <si>
-    <t>xMinyMin</t>
-  </si>
-  <si>
-    <t>barycenter</t>
-  </si>
-  <si>
-    <t>XMin, YMin (“Lower left”) corner (“Cell origin”)</t>
-  </si>
-  <si>
-    <t>xMaxyMax</t>
-  </si>
-  <si>
-    <t>xMaxyMin</t>
-  </si>
-  <si>
-    <t>xMinyMax</t>
-  </si>
-  <si>
     <t>XMax, YMax (“Upper right”) corner</t>
   </si>
   <si>
@@ -1938,13 +1920,7 @@
     <t>XMin, YMax (“Upper left”) corner</t>
   </si>
   <si>
-    <t>Not used in S-104</t>
-  </si>
-  <si>
     <t>Note that the definitions of the codes indicating the corners are in terms of X and Y grid coordinates relative to the grid origin. (This means that in a grid with its X axis directed from east to west and Y axis from north to south the “lower left” corner is different from the “lower left” corner in a grid with X axis directed west to east and Y axis south to north.)</t>
-  </si>
-  <si>
-    <t>See S-100 Table 10c-10 and sheet 104_2021 for enumeration</t>
   </si>
   <si>
     <t>Invalid Root Group Termination</t>
@@ -2180,6 +2156,52 @@
       </rPr>
       <t>Deleted because S-104 permits only regular grids</t>
     </r>
+  </si>
+  <si>
+    <t>LowerLeft</t>
+  </si>
+  <si>
+    <t>Barycenter</t>
+  </si>
+  <si>
+    <t>UpperRight</t>
+  </si>
+  <si>
+    <t>LowerRight</t>
+  </si>
+  <si>
+    <t>UpperLeft</t>
+  </si>
+  <si>
+    <t>Centroid of cell</t>
+  </si>
+  <si>
+    <t>Prohibited as a value of dataOffsetCode in datasets</t>
+  </si>
+  <si>
+    <t>See S-100 Table 10c-10 and sheet 104_2021 for enumeration codes and labels. Prohibited values may be used in defining the HDF5 enumeration type but must not be encoded as values of attribute dataOffsetCode</t>
+  </si>
+  <si>
+    <t>104_2026</t>
+  </si>
+  <si>
+    <t>Axes listed in axisNames are not latitude/longitude or northing/easting</t>
+  </si>
+  <si>
+    <t>Axis name error</t>
+  </si>
+  <si>
+    <t>Amend axisNames dataseet</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>Case-sensitive check.
+Validate combination too, e.g., latitude must be accompanied by longitude..</t>
+  </si>
+  <si>
+    <t>May require visual inspection</t>
   </si>
 </sst>
 </file>
@@ -2606,7 +2628,7 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2912,9 +2934,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2935,6 +2954,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -3321,14 +3344,14 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="127"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="126"/>
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3454,7 +3477,7 @@
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="123" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -3468,7 +3491,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="124"/>
+      <c r="B14" s="123"/>
       <c r="C14" s="29"/>
       <c r="D14" s="27"/>
       <c r="E14" s="30"/>
@@ -3476,7 +3499,7 @@
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="124"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="32"/>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
@@ -3484,7 +3507,7 @@
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="124"/>
+      <c r="B16" s="123"/>
       <c r="C16" s="22"/>
       <c r="D16" s="8"/>
       <c r="E16" s="21"/>
@@ -3492,7 +3515,7 @@
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="124"/>
+      <c r="B17" s="123"/>
       <c r="C17" s="23"/>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
@@ -3500,7 +3523,7 @@
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="124"/>
+      <c r="B18" s="123"/>
       <c r="C18" s="13"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -3536,7 +3559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3229863E-76E8-4615-9B5D-DE44E34EF947}">
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="46" customWidth="1"/>
@@ -3551,7 +3574,7 @@
     <col min="10" max="10" width="8.28515625" style="46" customWidth="1"/>
     <col min="11" max="11" width="8" style="46" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" style="36" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="112" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" style="112" customWidth="1"/>
     <col min="14" max="14" width="35.28515625" style="2" customWidth="1"/>
     <col min="15" max="15" width="18.140625" style="59" customWidth="1"/>
     <col min="16" max="16384" width="8.7109375" style="1"/>
@@ -3639,7 +3662,7 @@
       </c>
       <c r="M2" s="60"/>
       <c r="N2" s="36" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="O2" s="65" t="s">
         <v>205</v>
@@ -3676,11 +3699,11 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
       <c r="L3" s="74"/>
-      <c r="M3" s="123" t="s">
-        <v>585</v>
+      <c r="M3" s="122" t="s">
+        <v>577</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="O3" s="59" t="s">
         <v>43</v>
@@ -3752,11 +3775,11 @@
       </c>
       <c r="J5" s="36"/>
       <c r="K5" s="36"/>
-      <c r="M5" s="123" t="s">
-        <v>588</v>
+      <c r="M5" s="122" t="s">
+        <v>580</v>
       </c>
       <c r="N5" s="42" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="O5" s="59" t="s">
         <v>43</v>
@@ -3797,7 +3820,7 @@
       </c>
       <c r="M6" s="111"/>
       <c r="N6" s="42" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="O6" s="59" t="s">
         <v>207</v>
@@ -3838,7 +3861,7 @@
       </c>
       <c r="M7" s="111"/>
       <c r="N7" s="42" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="O7" s="59" t="s">
         <v>207</v>
@@ -3879,7 +3902,7 @@
       </c>
       <c r="M8" s="111"/>
       <c r="N8" s="42" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="O8" s="59" t="s">
         <v>208</v>
@@ -3956,7 +3979,7 @@
       </c>
       <c r="M10" s="111"/>
       <c r="N10" s="42" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>209</v>
@@ -3997,7 +4020,7 @@
       </c>
       <c r="M11" s="111"/>
       <c r="N11" s="42" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>209</v>
@@ -4035,7 +4058,7 @@
       <c r="K12" s="36"/>
       <c r="M12" s="111"/>
       <c r="N12" s="42" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>345</v>
@@ -4073,7 +4096,7 @@
       <c r="K13" s="36"/>
       <c r="M13" s="111"/>
       <c r="N13" s="42" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="O13" s="59" t="s">
         <v>210</v>
@@ -4111,7 +4134,7 @@
       <c r="K14" s="36"/>
       <c r="M14" s="111"/>
       <c r="N14" s="42" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="O14" s="59" t="s">
         <v>345</v>
@@ -4264,9 +4287,9 @@
         <v>388</v>
       </c>
       <c r="L18" s="93"/>
-      <c r="M18" s="123"/>
+      <c r="M18" s="122"/>
       <c r="N18" s="89" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="O18" s="98" t="s">
         <v>43</v>
@@ -4304,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="O19" s="59" t="s">
         <v>211</v>
@@ -4375,7 +4398,7 @@
       </c>
       <c r="L21" s="46"/>
       <c r="N21" s="2" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="O21" s="59" t="s">
         <v>211</v>
@@ -4445,7 +4468,7 @@
       </c>
       <c r="L23" s="46"/>
       <c r="N23" s="2" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="O23" s="59" t="s">
         <v>211</v>
@@ -4481,7 +4504,7 @@
       </c>
       <c r="L24" s="46"/>
       <c r="N24" s="2" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="O24" s="59" t="s">
         <v>211</v>
@@ -4634,7 +4657,7 @@
       <c r="C29" s="104" t="s">
         <v>253</v>
       </c>
-      <c r="D29" s="122" t="s">
+      <c r="D29" s="121" t="s">
         <v>255</v>
       </c>
       <c r="E29" s="94" t="s">
@@ -4728,65 +4751,62 @@
       </c>
       <c r="L31" s="46"/>
       <c r="N31" s="2" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="O31" s="59" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="36" t="s">
+    <row r="32" spans="1:15" s="128" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="93" t="s">
+        <v>593</v>
+      </c>
+      <c r="B32" s="100" t="s">
+        <v>389</v>
+      </c>
+      <c r="C32" s="104" t="s">
+        <v>595</v>
+      </c>
+      <c r="D32" s="121" t="s">
+        <v>594</v>
+      </c>
+      <c r="E32" s="94" t="s">
+        <v>596</v>
+      </c>
+      <c r="F32" s="94" t="s">
+        <v>204</v>
+      </c>
+      <c r="G32" s="97" t="s">
+        <v>597</v>
+      </c>
+      <c r="H32" s="104"/>
+      <c r="I32" s="93" t="s">
+        <v>388</v>
+      </c>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="129" t="s">
+        <v>598</v>
+      </c>
+      <c r="N32" s="89"/>
+      <c r="O32" s="98"/>
+    </row>
+    <row r="33" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="36" t="s">
         <v>422</v>
-      </c>
-      <c r="B32" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G32" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" s="68" t="s">
-        <v>233</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L32" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="36" t="s">
-        <v>423</v>
       </c>
       <c r="B33" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="D33" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="68" t="s">
-        <v>259</v>
+        <v>49</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>148</v>
       </c>
       <c r="F33" s="49" t="s">
         <v>204</v>
@@ -4810,55 +4830,59 @@
         <v>212</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="B34" s="75" t="s">
-        <v>390</v>
+        <v>423</v>
+      </c>
+      <c r="B34" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="D34" s="69" t="s">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="F34" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="H34" s="68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I34" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="L34" s="46"/>
-      <c r="N34" s="89"/>
+      <c r="L34" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>225</v>
+      </c>
       <c r="O34" s="59" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B35" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="C35" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="D35" s="62" t="s">
-        <v>350</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>150</v>
+      <c r="C35" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>349</v>
+      </c>
+      <c r="E35" s="68" t="s">
+        <v>149</v>
       </c>
       <c r="F35" s="49" t="s">
         <v>204</v>
@@ -4866,8 +4890,8 @@
       <c r="G35" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="H35" s="49" t="s">
-        <v>233</v>
+      <c r="H35" s="68" t="s">
+        <v>234</v>
       </c>
       <c r="I35" s="36" t="s">
         <v>242</v>
@@ -4875,24 +4899,24 @@
       <c r="L35" s="46"/>
       <c r="N35" s="89"/>
       <c r="O35" s="59" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B36" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>47</v>
+        <v>267</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="F36" s="49" t="s">
         <v>204</v>
@@ -4901,7 +4925,7 @@
         <v>139</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I36" s="36" t="s">
         <v>242</v>
@@ -4912,21 +4936,21 @@
         <v>211</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B37" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>336</v>
+        <v>47</v>
       </c>
       <c r="D37" s="62" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="F37" s="49" t="s">
         <v>204</v>
@@ -4935,7 +4959,7 @@
         <v>139</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I37" s="36" t="s">
         <v>242</v>
@@ -4946,21 +4970,21 @@
         <v>211</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B38" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="D38" s="62" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F38" s="49" t="s">
         <v>204</v>
@@ -4969,34 +4993,32 @@
         <v>139</v>
       </c>
       <c r="H38" s="49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I38" s="36" t="s">
         <v>242</v>
       </c>
       <c r="L38" s="46"/>
-      <c r="N38" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="O38" s="91" t="s">
+      <c r="N38" s="89"/>
+      <c r="O38" s="59" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B39" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>284</v>
+        <v>129</v>
       </c>
       <c r="D39" s="62" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>285</v>
+        <v>152</v>
       </c>
       <c r="F39" s="49" t="s">
         <v>204</v>
@@ -5005,228 +5027,227 @@
         <v>139</v>
       </c>
       <c r="H39" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="I39" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="L39" s="46"/>
+      <c r="N39" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="O39" s="98" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="178.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="B40" s="75" t="s">
+        <v>390</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>285</v>
+      </c>
+      <c r="F40" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="I39" s="36" t="s">
+      <c r="I40" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="J39" s="101" t="s">
+      <c r="J40" s="101" t="s">
         <v>388</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="121" t="s">
-        <v>560</v>
-      </c>
-      <c r="N39" s="89"/>
-      <c r="O39" s="59" t="s">
+      <c r="L40" s="46"/>
+      <c r="M40" s="89" t="s">
+        <v>592</v>
+      </c>
+      <c r="N40" s="89"/>
+      <c r="O40" s="59" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A40" s="93" t="s">
+    <row r="41" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A41" s="93" t="s">
         <v>538</v>
       </c>
-      <c r="B40" s="95" t="s">
+      <c r="B41" s="95" t="s">
         <v>391</v>
       </c>
-      <c r="C40" s="94" t="s">
+      <c r="C41" s="94" t="s">
         <v>535</v>
       </c>
-      <c r="D40" s="96" t="s">
+      <c r="D41" s="96" t="s">
         <v>536</v>
       </c>
-      <c r="E40" s="94" t="s">
+      <c r="E41" s="94" t="s">
         <v>537</v>
       </c>
-      <c r="F40" s="94" t="s">
+      <c r="F41" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="G40" s="97" t="s">
+      <c r="G41" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="H40" s="94"/>
-      <c r="I40" s="93" t="s">
+      <c r="H41" s="94"/>
+      <c r="I41" s="93" t="s">
         <v>388</v>
       </c>
-      <c r="J40" s="101"/>
-      <c r="K40" s="101"/>
-      <c r="L40" s="101"/>
-      <c r="M40" s="114"/>
-      <c r="N40" s="89" t="s">
-        <v>572</v>
-      </c>
-      <c r="O40" s="98"/>
-    </row>
-    <row r="41" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A41" s="36" t="s">
+      <c r="J41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="114"/>
+      <c r="N41" s="89" t="s">
+        <v>564</v>
+      </c>
+      <c r="O41" s="98"/>
+    </row>
+    <row r="42" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A42" s="36" t="s">
         <v>430</v>
       </c>
-      <c r="B41" s="75" t="s">
+      <c r="B42" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="C41" s="49" t="s">
+      <c r="C42" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="D41" s="64" t="s">
+      <c r="D42" s="64" t="s">
         <v>321</v>
       </c>
-      <c r="E41" s="49" t="s">
+      <c r="E42" s="49" t="s">
         <v>322</v>
-      </c>
-      <c r="F41" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="52" t="s">
-        <v>301</v>
-      </c>
-      <c r="H41" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="M41" s="111"/>
-      <c r="N41" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="36" t="s">
-        <v>431</v>
-      </c>
-      <c r="B42" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="C42" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="49" t="s">
-        <v>60</v>
       </c>
       <c r="F42" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G42" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="I42" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="M42" s="111"/>
+      <c r="N42" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="O42" s="59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="B43" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G43" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="H42" s="68" t="s">
+      <c r="H43" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="I42" s="36" t="s">
+      <c r="I43" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="L42" s="46"/>
-      <c r="N42" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="O42" s="59" t="s">
+      <c r="L43" s="46"/>
+      <c r="N43" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="O43" s="59" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A43" s="93" t="s">
+    <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A44" s="93" t="s">
         <v>432</v>
       </c>
-      <c r="B43" s="100" t="s">
+      <c r="B44" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="94" t="s">
+      <c r="C44" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="96" t="s">
+      <c r="D44" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="E43" s="94" t="s">
+      <c r="E44" s="94" t="s">
         <v>269</v>
       </c>
-      <c r="F43" s="94"/>
-      <c r="G43" s="97"/>
-      <c r="H43" s="94" t="s">
+      <c r="F44" s="94"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="94" t="s">
         <v>238</v>
       </c>
-      <c r="I43" s="93" t="s">
+      <c r="I44" s="93" t="s">
         <v>242</v>
       </c>
-      <c r="J43" s="101"/>
-      <c r="K43" s="101" t="s">
+      <c r="J44" s="101"/>
+      <c r="K44" s="101" t="s">
         <v>388</v>
       </c>
-      <c r="L43" s="101"/>
-      <c r="M43" s="114"/>
-      <c r="N43" s="89" t="s">
-        <v>590</v>
-      </c>
-      <c r="O43" s="98"/>
-    </row>
-    <row r="44" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="36" t="s">
+      <c r="L44" s="101"/>
+      <c r="M44" s="114"/>
+      <c r="N44" s="89" t="s">
+        <v>582</v>
+      </c>
+      <c r="O44" s="98"/>
+    </row>
+    <row r="45" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="36" t="s">
         <v>433</v>
-      </c>
-      <c r="B44" s="75" t="s">
-        <v>390</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>354</v>
-      </c>
-      <c r="D44" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E44" s="49" t="s">
-        <v>355</v>
-      </c>
-      <c r="F44" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G44" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="I44" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="N44" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="O44" s="59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="155.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="36" t="s">
-        <v>434</v>
       </c>
       <c r="B45" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>91</v>
+        <v>354</v>
       </c>
       <c r="D45" s="62" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="E45" s="49" t="s">
-        <v>53</v>
+        <v>355</v>
       </c>
       <c r="F45" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G45" s="52" t="s">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I45" s="36" t="s">
         <v>242</v>
@@ -5234,134 +5255,135 @@
       <c r="J45" s="36"/>
       <c r="K45" s="36"/>
       <c r="N45" s="2" t="s">
-        <v>357</v>
+        <v>566</v>
       </c>
       <c r="O45" s="59" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="155.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="36" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B46" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>307</v>
+        <v>91</v>
       </c>
       <c r="D46" s="62" t="s">
-        <v>490</v>
+        <v>356</v>
       </c>
       <c r="E46" s="49" t="s">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F46" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G46" s="52" t="s">
-        <v>118</v>
+        <v>270</v>
       </c>
       <c r="H46" s="49" t="s">
         <v>235</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="J46" s="36"/>
       <c r="K46" s="36"/>
-      <c r="N46" s="92" t="s">
+      <c r="N46" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="O46" s="59" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="B47" s="75" t="s">
+        <v>390</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>307</v>
+      </c>
+      <c r="D47" s="62" t="s">
+        <v>490</v>
+      </c>
+      <c r="E47" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="F47" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="H47" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="N47" s="92" t="s">
         <v>309</v>
       </c>
-      <c r="O46" s="59" t="s">
+      <c r="O47" s="59" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="93" t="s">
+    <row r="48" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="93" t="s">
         <v>489</v>
       </c>
-      <c r="B47" s="95" t="s">
+      <c r="B48" s="95" t="s">
         <v>390</v>
       </c>
-      <c r="C47" s="94" t="s">
+      <c r="C48" s="94" t="s">
         <v>492</v>
       </c>
-      <c r="D47" s="96" t="s">
+      <c r="D48" s="96" t="s">
         <v>494</v>
       </c>
-      <c r="E47" s="94" t="s">
+      <c r="E48" s="94" t="s">
         <v>491</v>
       </c>
-      <c r="F47" s="94" t="s">
+      <c r="F48" s="94" t="s">
         <v>204</v>
       </c>
-      <c r="G47" s="97" t="s">
+      <c r="G48" s="97" t="s">
         <v>232</v>
       </c>
-      <c r="H47" s="94" t="s">
+      <c r="H48" s="94" t="s">
         <v>235</v>
       </c>
-      <c r="I47" s="93" t="s">
+      <c r="I48" s="93" t="s">
         <v>493</v>
       </c>
-      <c r="J47" s="93"/>
-      <c r="K47" s="93"/>
-      <c r="L47" s="93"/>
-      <c r="M47" s="114"/>
-      <c r="N47" s="89"/>
-      <c r="O47" s="98"/>
-    </row>
-    <row r="48" spans="1:15" ht="52.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="36" t="s">
+      <c r="J48" s="93"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="93"/>
+      <c r="M48" s="114"/>
+      <c r="N48" s="89"/>
+      <c r="O48" s="98"/>
+    </row>
+    <row r="49" spans="1:15" ht="52.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="36" t="s">
         <v>436</v>
       </c>
-      <c r="B48" s="75" t="s">
+      <c r="B49" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C49" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D49" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="E48" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H48" s="63" t="s">
-        <v>233</v>
-      </c>
-      <c r="I48" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="M48" s="115"/>
-      <c r="N48" s="89"/>
-      <c r="O48" s="59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="36" t="s">
-        <v>437</v>
-      </c>
-      <c r="B49" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="62" t="s">
-        <v>358</v>
-      </c>
-      <c r="E49" s="49" t="s">
+      <c r="E49" s="63" t="s">
         <v>56</v>
       </c>
       <c r="F49" s="49" t="s">
@@ -5370,7 +5392,7 @@
       <c r="G49" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H49" s="49" t="s">
+      <c r="H49" s="63" t="s">
         <v>233</v>
       </c>
       <c r="I49" s="36" t="s">
@@ -5378,27 +5400,27 @@
       </c>
       <c r="J49" s="36"/>
       <c r="K49" s="36"/>
-      <c r="M49" s="116"/>
+      <c r="M49" s="115"/>
       <c r="N49" s="89"/>
       <c r="O49" s="59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="36" t="s">
-        <v>438</v>
-      </c>
-      <c r="B50" s="75" t="s">
-        <v>390</v>
-      </c>
-      <c r="C50" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" s="71" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="70" t="s">
-        <v>153</v>
+        <v>437</v>
+      </c>
+      <c r="B50" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="C50" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="62" t="s">
+        <v>358</v>
+      </c>
+      <c r="E50" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F50" s="49" t="s">
         <v>204</v>
@@ -5414,26 +5436,27 @@
       </c>
       <c r="J50" s="36"/>
       <c r="K50" s="36"/>
+      <c r="M50" s="116"/>
       <c r="N50" s="89"/>
       <c r="O50" s="59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A51" s="36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B51" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C51" s="70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D51" s="71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E51" s="70" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F51" s="49" t="s">
         <v>204</v>
@@ -5442,32 +5465,33 @@
         <v>118</v>
       </c>
       <c r="H51" s="49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I51" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J51" s="36"/>
       <c r="K51" s="36"/>
+      <c r="N51" s="89"/>
       <c r="O51" s="59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A52" s="36" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B52" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C52" s="70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D52" s="71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E52" s="70" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="F52" s="49" t="s">
         <v>204</v>
@@ -5476,30 +5500,29 @@
         <v>118</v>
       </c>
       <c r="H52" s="49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I52" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J52" s="36"/>
       <c r="K52" s="36"/>
-      <c r="N52" s="89"/>
       <c r="O52" s="59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A53" s="36" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B53" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C53" s="70" t="s">
-        <v>256</v>
+        <v>96</v>
       </c>
       <c r="D53" s="71" t="s">
-        <v>257</v>
+        <v>115</v>
       </c>
       <c r="E53" s="70" t="s">
         <v>56</v>
@@ -5511,35 +5534,33 @@
         <v>118</v>
       </c>
       <c r="H53" s="49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="J53" s="36"/>
       <c r="K53" s="36"/>
-      <c r="N53" s="2" t="s">
-        <v>575</v>
-      </c>
+      <c r="N53" s="89"/>
       <c r="O53" s="59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="36" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B54" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="C54" s="49" t="s">
-        <v>286</v>
-      </c>
-      <c r="D54" s="62" t="s">
-        <v>287</v>
-      </c>
-      <c r="E54" s="49" t="s">
-        <v>288</v>
+      <c r="C54" s="70" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" s="71" t="s">
+        <v>257</v>
+      </c>
+      <c r="E54" s="70" t="s">
+        <v>56</v>
       </c>
       <c r="F54" s="49" t="s">
         <v>204</v>
@@ -5553,30 +5574,30 @@
       <c r="I54" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="112"/>
-      <c r="N54" s="89"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="N54" s="2" t="s">
+        <v>567</v>
+      </c>
       <c r="O54" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A55" s="36" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="D55" s="62" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="E55" s="49" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
       <c r="F55" s="49" t="s">
         <v>204</v>
@@ -5590,27 +5611,30 @@
       <c r="I55" s="36" t="s">
         <v>258</v>
       </c>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
       <c r="L55" s="46"/>
+      <c r="M55" s="112"/>
       <c r="N55" s="89"/>
       <c r="O55" s="59" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B56" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>97</v>
+        <v>333</v>
       </c>
       <c r="D56" s="62" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="E56" s="49" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
       <c r="F56" s="49" t="s">
         <v>204</v>
@@ -5619,30 +5643,29 @@
         <v>118</v>
       </c>
       <c r="H56" s="49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
+        <v>258</v>
+      </c>
+      <c r="L56" s="46"/>
       <c r="N56" s="89"/>
       <c r="O56" s="59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A57" s="36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B57" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="62" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E57" s="49" t="s">
         <v>56</v>
@@ -5666,21 +5689,21 @@
         <v>214</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="36" t="s">
-        <v>446</v>
-      </c>
-      <c r="B58" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="C58" s="70" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="E58" s="70" t="s">
-        <v>55</v>
+        <v>445</v>
+      </c>
+      <c r="B58" s="75" t="s">
+        <v>390</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="62" t="s">
+        <v>360</v>
+      </c>
+      <c r="E58" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F58" s="49" t="s">
         <v>204</v>
@@ -5688,36 +5711,34 @@
       <c r="G58" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H58" s="70" t="s">
-        <v>235</v>
+      <c r="H58" s="49" t="s">
+        <v>233</v>
       </c>
       <c r="I58" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J58" s="36"/>
       <c r="K58" s="36"/>
-      <c r="N58" s="2" t="s">
-        <v>226</v>
-      </c>
+      <c r="N58" s="89"/>
       <c r="O58" s="59" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A59" s="36" t="s">
-        <v>447</v>
-      </c>
-      <c r="B59" s="75" t="s">
-        <v>390</v>
+        <v>446</v>
+      </c>
+      <c r="B59" s="61" t="s">
+        <v>391</v>
       </c>
       <c r="C59" s="70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D59" s="71" t="s">
-        <v>362</v>
-      </c>
-      <c r="E59" s="49" t="s">
-        <v>56</v>
+        <v>361</v>
+      </c>
+      <c r="E59" s="70" t="s">
+        <v>55</v>
       </c>
       <c r="F59" s="49" t="s">
         <v>204</v>
@@ -5726,35 +5747,35 @@
         <v>118</v>
       </c>
       <c r="H59" s="70" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I59" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J59" s="36"/>
       <c r="K59" s="36"/>
-      <c r="N59" s="92" t="s">
-        <v>576</v>
+      <c r="N59" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="O59" s="59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="36" t="s">
-        <v>448</v>
-      </c>
-      <c r="B60" s="61" t="s">
-        <v>391</v>
+        <v>447</v>
+      </c>
+      <c r="B60" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C60" s="70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>363</v>
-      </c>
-      <c r="E60" s="70" t="s">
-        <v>57</v>
+        <v>362</v>
+      </c>
+      <c r="E60" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="F60" s="49" t="s">
         <v>204</v>
@@ -5763,35 +5784,35 @@
         <v>118</v>
       </c>
       <c r="H60" s="70" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I60" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J60" s="36"/>
       <c r="K60" s="36"/>
-      <c r="N60" s="2" t="s">
-        <v>227</v>
+      <c r="N60" s="92" t="s">
+        <v>568</v>
       </c>
       <c r="O60" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="36" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B61" s="61" t="s">
         <v>391</v>
       </c>
-      <c r="C61" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" s="62" t="s">
-        <v>364</v>
-      </c>
-      <c r="E61" s="49" t="s">
-        <v>58</v>
+      <c r="C61" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="D61" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="E61" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="F61" s="49" t="s">
         <v>204</v>
@@ -5799,7 +5820,7 @@
       <c r="G61" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H61" s="49" t="s">
+      <c r="H61" s="70" t="s">
         <v>235</v>
       </c>
       <c r="I61" s="36" t="s">
@@ -5808,27 +5829,27 @@
       <c r="J61" s="36"/>
       <c r="K61" s="36"/>
       <c r="N61" s="2" t="s">
-        <v>577</v>
+        <v>227</v>
       </c>
       <c r="O61" s="59" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A62" s="36" t="s">
-        <v>450</v>
-      </c>
-      <c r="B62" s="75" t="s">
-        <v>390</v>
+        <v>449</v>
+      </c>
+      <c r="B62" s="61" t="s">
+        <v>391</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" s="62" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F62" s="49" t="s">
         <v>204</v>
@@ -5837,33 +5858,35 @@
         <v>118</v>
       </c>
       <c r="H62" s="49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I62" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J62" s="36"/>
       <c r="K62" s="36"/>
-      <c r="N62" s="89"/>
+      <c r="N62" s="2" t="s">
+        <v>569</v>
+      </c>
       <c r="O62" s="59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A63" s="36" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B63" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" s="62" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F63" s="49" t="s">
         <v>204</v>
@@ -5871,36 +5894,34 @@
       <c r="G63" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H63" s="68" t="s">
-        <v>235</v>
+      <c r="H63" s="49" t="s">
+        <v>233</v>
       </c>
       <c r="I63" s="36" t="s">
         <v>242</v>
       </c>
       <c r="J63" s="36"/>
       <c r="K63" s="36"/>
-      <c r="N63" s="2" t="s">
-        <v>531</v>
-      </c>
+      <c r="N63" s="89"/>
       <c r="O63" s="59" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" s="81" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A64" s="36" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B64" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>289</v>
+        <v>104</v>
       </c>
       <c r="D64" s="62" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>290</v>
+        <v>59</v>
       </c>
       <c r="F64" s="49" t="s">
         <v>204</v>
@@ -5908,36 +5929,36 @@
       <c r="G64" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H64" s="49" t="s">
-        <v>234</v>
+      <c r="H64" s="68" t="s">
+        <v>235</v>
       </c>
       <c r="I64" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-      <c r="M64" s="112"/>
-      <c r="N64" s="89"/>
+        <v>242</v>
+      </c>
+      <c r="J64" s="36"/>
+      <c r="K64" s="36"/>
+      <c r="N64" s="2" t="s">
+        <v>531</v>
+      </c>
       <c r="O64" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" s="81" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B65" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D65" s="62" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F65" s="49" t="s">
         <v>204</v>
@@ -5951,33 +5972,36 @@
       <c r="I65" s="36" t="s">
         <v>258</v>
       </c>
+      <c r="J65" s="46"/>
+      <c r="K65" s="46"/>
       <c r="L65" s="46"/>
+      <c r="M65" s="112"/>
       <c r="N65" s="89"/>
       <c r="O65" s="59" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="81" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" s="36" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B66" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D66" s="62" t="s">
-        <v>579</v>
+        <v>303</v>
       </c>
       <c r="E66" s="49" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="F66" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G66" s="52" t="s">
-        <v>311</v>
+        <v>118</v>
       </c>
       <c r="H66" s="49" t="s">
         <v>234</v>
@@ -5985,34 +6009,27 @@
       <c r="I66" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="J66" s="93" t="s">
-        <v>388</v>
-      </c>
-      <c r="K66" s="36"/>
-      <c r="L66" s="36"/>
-      <c r="M66" s="112"/>
-      <c r="N66" s="89" t="s">
-        <v>578</v>
-      </c>
+      <c r="L66" s="46"/>
+      <c r="N66" s="89"/>
       <c r="O66" s="59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" s="81" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A67" s="36" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B67" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D67" s="62" t="s">
-        <v>314</v>
+        <v>571</v>
       </c>
       <c r="E67" s="49" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F67" s="49" t="s">
         <v>204</v>
@@ -6026,59 +6043,69 @@
       <c r="I67" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="J67" s="93"/>
+      <c r="J67" s="93" t="s">
+        <v>388</v>
+      </c>
       <c r="K67" s="36"/>
-      <c r="N67" s="89"/>
+      <c r="L67" s="36"/>
+      <c r="M67" s="112"/>
+      <c r="N67" s="89" t="s">
+        <v>570</v>
+      </c>
       <c r="O67" s="59" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A68" s="36" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B68" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>105</v>
+        <v>313</v>
       </c>
       <c r="D68" s="62" t="s">
-        <v>116</v>
+        <v>314</v>
       </c>
       <c r="E68" s="49" t="s">
-        <v>155</v>
+        <v>315</v>
       </c>
       <c r="F68" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G68" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="H68" s="68" t="s">
-        <v>233</v>
+        <v>311</v>
+      </c>
+      <c r="H68" s="49" t="s">
+        <v>234</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L68" s="46"/>
+        <v>258</v>
+      </c>
+      <c r="J68" s="93"/>
+      <c r="K68" s="36"/>
       <c r="N68" s="89"/>
-    </row>
-    <row r="69" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="O68" s="59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A69" s="36" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B69" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>367</v>
+        <v>105</v>
       </c>
       <c r="D69" s="62" t="s">
-        <v>368</v>
-      </c>
-      <c r="E69" s="68" t="s">
-        <v>54</v>
+        <v>116</v>
+      </c>
+      <c r="E69" s="49" t="s">
+        <v>155</v>
       </c>
       <c r="F69" s="49" t="s">
         <v>204</v>
@@ -6086,7 +6113,7 @@
       <c r="G69" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="H69" s="49" t="s">
+      <c r="H69" s="68" t="s">
         <v>233</v>
       </c>
       <c r="I69" s="36" t="s">
@@ -6097,137 +6124,130 @@
     </row>
     <row r="70" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A70" s="36" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B70" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>323</v>
-      </c>
-      <c r="D70" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="E70" s="49" t="s">
-        <v>325</v>
+        <v>367</v>
+      </c>
+      <c r="D70" s="62" t="s">
+        <v>368</v>
+      </c>
+      <c r="E70" s="68" t="s">
+        <v>54</v>
       </c>
       <c r="F70" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G70" s="52" t="s">
-        <v>301</v>
+        <v>118</v>
       </c>
       <c r="H70" s="49" t="s">
         <v>233</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="J70" s="36"/>
-      <c r="K70" s="36"/>
-      <c r="M70" s="111"/>
-      <c r="N70" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O70" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="L70" s="46"/>
+      <c r="N70" s="89"/>
+    </row>
+    <row r="71" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="B71" s="61" t="s">
-        <v>391</v>
+        <v>458</v>
+      </c>
+      <c r="B71" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="68" t="s">
-        <v>60</v>
+        <v>323</v>
+      </c>
+      <c r="D71" s="64" t="s">
+        <v>324</v>
+      </c>
+      <c r="E71" s="49" t="s">
+        <v>325</v>
       </c>
       <c r="F71" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G71" s="52" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="H71" s="49" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L71" s="46"/>
+        <v>258</v>
+      </c>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="M71" s="111"/>
       <c r="N71" s="2" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="O71" s="59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" ht="127.5" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D72" s="62" t="s">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="E72" s="68" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="F72" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G72" s="52" t="s">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="H72" s="49" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I72" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="L72" s="36" t="b">
-        <v>1</v>
-      </c>
+      <c r="L72" s="46"/>
       <c r="N72" s="2" t="s">
-        <v>582</v>
+        <v>271</v>
       </c>
       <c r="O72" s="59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" s="81" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A73" s="36" t="s">
-        <v>461</v>
-      </c>
-      <c r="B73" s="75" t="s">
-        <v>390</v>
+        <v>460</v>
+      </c>
+      <c r="B73" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="C73" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D73" s="62" t="s">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="E73" s="68" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="F73" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G73" s="52" t="s">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="H73" s="49" t="s">
         <v>233</v>
@@ -6235,36 +6255,37 @@
       <c r="I73" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
-      <c r="L73" s="46"/>
-      <c r="M73" s="112"/>
-      <c r="N73" s="89"/>
+      <c r="L73" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>574</v>
+      </c>
       <c r="O73" s="59" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" s="81" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A74" s="36" t="s">
-        <v>462</v>
-      </c>
-      <c r="B74" s="61" t="s">
-        <v>391</v>
+        <v>461</v>
+      </c>
+      <c r="B74" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D74" s="62" t="s">
-        <v>369</v>
+        <v>117</v>
       </c>
       <c r="E74" s="68" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="F74" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G74" s="52" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="H74" s="49" t="s">
         <v>233</v>
@@ -6278,30 +6299,30 @@
       <c r="M74" s="112"/>
       <c r="N74" s="89"/>
       <c r="O74" s="59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" s="81" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A75" s="36" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B75" s="61" t="s">
         <v>391</v>
       </c>
       <c r="C75" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D75" s="62" t="s">
-        <v>262</v>
+        <v>369</v>
       </c>
       <c r="E75" s="68" t="s">
-        <v>157</v>
+        <v>370</v>
       </c>
       <c r="F75" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G75" s="52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H75" s="49" t="s">
         <v>233</v>
@@ -6318,90 +6339,93 @@
         <v>217</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A76" s="93" t="s">
+    <row r="76" spans="1:15" s="81" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="36" t="s">
+        <v>463</v>
+      </c>
+      <c r="B76" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="C76" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D76" s="62" t="s">
+        <v>262</v>
+      </c>
+      <c r="E76" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G76" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="H76" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="I76" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="46"/>
+      <c r="M76" s="112"/>
+      <c r="N76" s="89"/>
+      <c r="O76" s="59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" s="81" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A77" s="93" t="s">
         <v>464</v>
       </c>
-      <c r="B76" s="100" t="s">
+      <c r="B77" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="C76" s="94" t="s">
+      <c r="C77" s="94" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="96" t="s">
+      <c r="D77" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="E76" s="104" t="s">
+      <c r="E77" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="F76" s="94"/>
-      <c r="G76" s="97"/>
-      <c r="H76" s="94" t="s">
+      <c r="F77" s="94"/>
+      <c r="G77" s="97"/>
+      <c r="H77" s="94" t="s">
         <v>238</v>
       </c>
-      <c r="I76" s="93" t="s">
+      <c r="I77" s="93" t="s">
         <v>242</v>
       </c>
-      <c r="J76" s="101"/>
-      <c r="K76" s="101" t="s">
+      <c r="J77" s="101"/>
+      <c r="K77" s="101" t="s">
         <v>388</v>
       </c>
-      <c r="L76" s="101"/>
-      <c r="M76" s="114"/>
-      <c r="N76" s="89" t="s">
-        <v>590</v>
-      </c>
-      <c r="O76" s="98"/>
-    </row>
-    <row r="77" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A77" s="36" t="s">
+      <c r="L77" s="101"/>
+      <c r="M77" s="114"/>
+      <c r="N77" s="89" t="s">
+        <v>582</v>
+      </c>
+      <c r="O77" s="98"/>
+    </row>
+    <row r="78" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="36" t="s">
         <v>465</v>
       </c>
-      <c r="B77" s="61" t="s">
+      <c r="B78" s="61" t="s">
         <v>389</v>
       </c>
-      <c r="C77" s="49" t="s">
+      <c r="C78" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="D77" s="62" t="s">
+      <c r="D78" s="62" t="s">
         <v>371</v>
       </c>
-      <c r="E77" s="49" t="s">
+      <c r="E78" s="49" t="s">
         <v>56</v>
-      </c>
-      <c r="F77" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G77" s="52" t="s">
-        <v>372</v>
-      </c>
-      <c r="H77" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="I77" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L77" s="46"/>
-      <c r="N77" s="89"/>
-      <c r="O77" s="59" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" s="81" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="36" t="s">
-        <v>466</v>
-      </c>
-      <c r="B78" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="C78" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="D78" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="E78" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="F78" s="49" t="s">
         <v>204</v>
@@ -6410,71 +6434,71 @@
         <v>372</v>
       </c>
       <c r="H78" s="49" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I78" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
       <c r="L78" s="46"/>
-      <c r="M78" s="112"/>
-      <c r="N78" s="2" t="s">
-        <v>220</v>
-      </c>
+      <c r="N78" s="89"/>
       <c r="O78" s="59" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" s="81" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="36" t="s">
-        <v>467</v>
-      </c>
-      <c r="B79" s="75" t="s">
-        <v>390</v>
+        <v>466</v>
+      </c>
+      <c r="B79" s="61" t="s">
+        <v>391</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="D79" s="62" t="s">
-        <v>295</v>
+        <v>168</v>
       </c>
       <c r="E79" s="49" t="s">
-        <v>296</v>
+        <v>173</v>
       </c>
       <c r="F79" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G79" s="52" t="s">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="H79" s="49" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>258</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
       <c r="L79" s="46"/>
-      <c r="N79" s="89"/>
+      <c r="M79" s="112"/>
+      <c r="N79" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="O79" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="36" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B80" s="75" t="s">
         <v>390</v>
       </c>
       <c r="C80" s="49" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D80" s="62" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E80" s="49" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F80" s="49" t="s">
         <v>204</v>
@@ -6494,64 +6518,61 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="36" t="s">
-        <v>469</v>
-      </c>
-      <c r="B81" s="61" t="s">
-        <v>389</v>
+        <v>468</v>
+      </c>
+      <c r="B81" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
       <c r="D81" s="62" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
       <c r="E81" s="49" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="F81" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G81" s="52" t="s">
-        <v>89</v>
+        <v>297</v>
       </c>
       <c r="H81" s="49" t="s">
         <v>233</v>
       </c>
       <c r="I81" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
+        <v>258</v>
+      </c>
       <c r="L81" s="46"/>
-      <c r="M81" s="112"/>
       <c r="N81" s="89"/>
       <c r="O81" s="59" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" s="81" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A82" s="36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B82" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C82" s="49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D82" s="62" t="s">
-        <v>374</v>
+        <v>169</v>
       </c>
       <c r="E82" s="49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F82" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G82" s="52" t="s">
-        <v>375</v>
+        <v>89</v>
       </c>
       <c r="H82" s="49" t="s">
         <v>233</v>
@@ -6565,23 +6586,23 @@
       <c r="M82" s="112"/>
       <c r="N82" s="89"/>
       <c r="O82" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:15" s="81" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A83" s="36" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B83" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C83" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="D83" s="72" t="s">
-        <v>376</v>
-      </c>
-      <c r="E83" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="D83" s="62" t="s">
+        <v>374</v>
+      </c>
+      <c r="E83" s="49" t="s">
         <v>66</v>
       </c>
       <c r="F83" s="49" t="s">
@@ -6605,55 +6626,57 @@
         <v>219</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="65.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" s="81" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A84" s="36" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B84" s="61" t="s">
         <v>389</v>
       </c>
-      <c r="C84" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="D84" s="69" t="s">
-        <v>377</v>
-      </c>
-      <c r="E84" s="68" t="s">
+      <c r="C84" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="72" t="s">
+        <v>376</v>
+      </c>
+      <c r="E84" s="73" t="s">
         <v>66</v>
       </c>
       <c r="F84" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G84" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="H84" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="H84" s="49" t="s">
         <v>233</v>
       </c>
       <c r="I84" s="36" t="s">
         <v>242</v>
       </c>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
       <c r="L84" s="46"/>
-      <c r="M84" s="113"/>
+      <c r="M84" s="112"/>
       <c r="N84" s="89"/>
       <c r="O84" s="59" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" ht="65.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B85" s="61" t="s">
         <v>389</v>
       </c>
-      <c r="C85" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="D85" s="72" t="s">
-        <v>170</v>
-      </c>
-      <c r="E85" s="49" t="s">
+      <c r="C85" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="D85" s="69" t="s">
+        <v>377</v>
+      </c>
+      <c r="E85" s="68" t="s">
         <v>66</v>
       </c>
       <c r="F85" s="49" t="s">
@@ -6662,77 +6685,76 @@
       <c r="G85" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="H85" s="49" t="s">
+      <c r="H85" s="68" t="s">
         <v>233</v>
       </c>
       <c r="I85" s="36" t="s">
         <v>242</v>
       </c>
       <c r="L85" s="46"/>
-      <c r="N85" s="2" t="s">
-        <v>221</v>
-      </c>
+      <c r="M85" s="113"/>
+      <c r="N85" s="89"/>
       <c r="O85" s="59" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="36" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B86" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C86" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="D86" s="62" t="s">
-        <v>379</v>
+        <v>164</v>
+      </c>
+      <c r="D86" s="72" t="s">
+        <v>170</v>
       </c>
       <c r="E86" s="49" t="s">
-        <v>380</v>
+        <v>66</v>
       </c>
       <c r="F86" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G86" s="52" t="s">
-        <v>228</v>
+        <v>68</v>
       </c>
       <c r="H86" s="49" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I86" s="36" t="s">
         <v>242</v>
       </c>
       <c r="L86" s="46"/>
       <c r="N86" s="2" t="s">
-        <v>581</v>
+        <v>221</v>
       </c>
       <c r="O86" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="36" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B87" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D87" s="62" t="s">
-        <v>382</v>
-      </c>
-      <c r="E87" s="68" t="s">
-        <v>67</v>
+        <v>379</v>
+      </c>
+      <c r="E87" s="49" t="s">
+        <v>380</v>
       </c>
       <c r="F87" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G87" s="52" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="H87" s="49" t="s">
         <v>236</v>
@@ -6742,24 +6764,24 @@
       </c>
       <c r="L87" s="46"/>
       <c r="N87" s="2" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="O87" s="59" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B88" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D88" s="62" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E88" s="68" t="s">
         <v>67</v>
@@ -6768,7 +6790,7 @@
         <v>204</v>
       </c>
       <c r="G88" s="52" t="s">
-        <v>385</v>
+        <v>176</v>
       </c>
       <c r="H88" s="49" t="s">
         <v>236</v>
@@ -6778,24 +6800,24 @@
       </c>
       <c r="L88" s="46"/>
       <c r="N88" s="2" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="O88" s="59" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A89" s="36" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B89" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C89" s="49" t="s">
-        <v>293</v>
+        <v>383</v>
       </c>
       <c r="D89" s="62" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="E89" s="68" t="s">
         <v>67</v>
@@ -6804,34 +6826,34 @@
         <v>204</v>
       </c>
       <c r="G89" s="52" t="s">
-        <v>176</v>
+        <v>385</v>
       </c>
       <c r="H89" s="49" t="s">
         <v>236</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="L89" s="46"/>
       <c r="N89" s="2" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="O89" s="59" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A90" s="36" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B90" s="61" t="s">
         <v>389</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>63</v>
+        <v>293</v>
       </c>
       <c r="D90" s="62" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="E90" s="68" t="s">
         <v>67</v>
@@ -6840,98 +6862,106 @@
         <v>204</v>
       </c>
       <c r="G90" s="52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H90" s="49" t="s">
         <v>236</v>
       </c>
       <c r="I90" s="36" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="L90" s="46"/>
-      <c r="N90" s="89"/>
-    </row>
-    <row r="91" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N90" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="O90" s="59" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="36" t="s">
-        <v>479</v>
-      </c>
-      <c r="B91" s="75" t="s">
-        <v>390</v>
+        <v>478</v>
+      </c>
+      <c r="B91" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="C91" s="49" t="s">
-        <v>326</v>
-      </c>
-      <c r="D91" s="64" t="s">
-        <v>327</v>
-      </c>
-      <c r="E91" s="49" t="s">
-        <v>328</v>
+        <v>63</v>
+      </c>
+      <c r="D91" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="E91" s="68" t="s">
+        <v>67</v>
       </c>
       <c r="F91" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G91" s="52" t="s">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="H91" s="49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I91" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="J91" s="36"/>
-      <c r="K91" s="36"/>
-      <c r="M91" s="111"/>
-      <c r="N91" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O91" s="59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="L91" s="46"/>
+      <c r="N91" s="89"/>
+    </row>
+    <row r="92" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="36" t="s">
-        <v>480</v>
-      </c>
-      <c r="B92" s="61" t="s">
-        <v>391</v>
+        <v>479</v>
+      </c>
+      <c r="B92" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C92" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="D92" s="62" t="s">
-        <v>171</v>
+        <v>326</v>
+      </c>
+      <c r="D92" s="64" t="s">
+        <v>327</v>
       </c>
       <c r="E92" s="49" t="s">
-        <v>60</v>
+        <v>328</v>
       </c>
       <c r="F92" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="G92" s="52"/>
+      <c r="G92" s="52" t="s">
+        <v>301</v>
+      </c>
       <c r="H92" s="49" t="s">
         <v>233</v>
       </c>
       <c r="I92" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="L92" s="46"/>
-    </row>
-    <row r="93" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="J92" s="36"/>
+      <c r="K92" s="36"/>
+      <c r="M92" s="111"/>
+      <c r="N92" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="O92" s="59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="36" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B93" s="61" t="s">
         <v>391</v>
       </c>
       <c r="C93" s="49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D93" s="62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E93" s="49" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="F93" s="49" t="s">
         <v>204</v>
@@ -6945,21 +6975,21 @@
       </c>
       <c r="L93" s="46"/>
     </row>
-    <row r="94" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B94" s="61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C94" s="49" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D94" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="E94" s="68" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="E94" s="49" t="s">
+        <v>174</v>
       </c>
       <c r="F94" s="49" t="s">
         <v>204</v>
@@ -6971,70 +7001,63 @@
       <c r="I94" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="K94" s="101" t="s">
+      <c r="L94" s="46"/>
+    </row>
+    <row r="95" spans="1:15" ht="141.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="B95" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="C95" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D95" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="E95" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="F95" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G95" s="52"/>
+      <c r="H95" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="I95" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="K95" s="101" t="s">
         <v>388</v>
       </c>
-      <c r="L94" s="46"/>
-      <c r="M94" s="114" t="s">
-        <v>591</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="O94" s="59" t="s">
+      <c r="L95" s="46"/>
+      <c r="M95" s="114" t="s">
+        <v>583</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="O95" s="59" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="93" t="s">
-        <v>524</v>
-      </c>
-      <c r="B95" s="100" t="s">
-        <v>389</v>
-      </c>
-      <c r="C95" s="94" t="s">
-        <v>528</v>
-      </c>
-      <c r="D95" s="96" t="s">
-        <v>525</v>
-      </c>
-      <c r="E95" s="104" t="s">
-        <v>526</v>
-      </c>
-      <c r="F95" s="94" t="s">
-        <v>68</v>
-      </c>
-      <c r="G95" s="97" t="s">
-        <v>527</v>
-      </c>
-      <c r="H95" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="I95" s="93" t="s">
-        <v>388</v>
-      </c>
-      <c r="J95" s="101"/>
-      <c r="K95" s="101"/>
-      <c r="L95" s="101"/>
-      <c r="M95" s="114"/>
-      <c r="N95" s="89"/>
-      <c r="O95" s="98"/>
     </row>
     <row r="96" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="93" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B96" s="100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C96" s="94" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="D96" s="96" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="E96" s="104" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="F96" s="94" t="s">
         <v>68</v>
@@ -7042,7 +7065,9 @@
       <c r="G96" s="97" t="s">
         <v>527</v>
       </c>
-      <c r="H96" s="94"/>
+      <c r="H96" s="94" t="s">
+        <v>233</v>
+      </c>
       <c r="I96" s="93" t="s">
         <v>388</v>
       </c>
@@ -7053,61 +7078,60 @@
       <c r="N96" s="89"/>
       <c r="O96" s="98"/>
     </row>
-    <row r="97" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A97" s="79" t="s">
-        <v>483</v>
-      </c>
-      <c r="B97" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="C97" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="D97" s="62" t="s">
-        <v>264</v>
-      </c>
-      <c r="E97" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="F97" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G97" s="52" t="s">
-        <v>276</v>
-      </c>
-      <c r="H97" s="49" t="s">
-        <v>202</v>
-      </c>
+    <row r="97" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="93" t="s">
+        <v>540</v>
+      </c>
+      <c r="B97" s="100" t="s">
+        <v>390</v>
+      </c>
+      <c r="C97" s="94" t="s">
+        <v>542</v>
+      </c>
+      <c r="D97" s="96" t="s">
+        <v>541</v>
+      </c>
+      <c r="E97" s="104" t="s">
+        <v>544</v>
+      </c>
+      <c r="F97" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="G97" s="97" t="s">
+        <v>527</v>
+      </c>
+      <c r="H97" s="94"/>
       <c r="I97" s="93" t="s">
-        <v>246</v>
-      </c>
-      <c r="L97" s="46"/>
+        <v>388</v>
+      </c>
+      <c r="J97" s="101"/>
+      <c r="K97" s="101"/>
+      <c r="L97" s="101"/>
+      <c r="M97" s="114"/>
       <c r="N97" s="89"/>
-      <c r="O97" s="59" t="s">
-        <v>386</v>
-      </c>
+      <c r="O97" s="98"/>
     </row>
     <row r="98" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="79" t="s">
-        <v>484</v>
-      </c>
-      <c r="B98" s="75" t="s">
-        <v>390</v>
+        <v>483</v>
+      </c>
+      <c r="B98" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="C98" s="49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D98" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="E98" s="73" t="s">
-        <v>200</v>
+        <v>264</v>
+      </c>
+      <c r="E98" s="49" t="s">
+        <v>199</v>
       </c>
       <c r="F98" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G98" s="52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H98" s="49" t="s">
         <v>202</v>
@@ -7121,27 +7145,27 @@
         <v>386</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="79" t="s">
-        <v>485</v>
-      </c>
-      <c r="B99" s="61" t="s">
-        <v>391</v>
+        <v>484</v>
+      </c>
+      <c r="B99" s="75" t="s">
+        <v>390</v>
       </c>
       <c r="C99" s="49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D99" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="E99" s="49" t="s">
-        <v>201</v>
+        <v>265</v>
+      </c>
+      <c r="E99" s="73" t="s">
+        <v>200</v>
       </c>
       <c r="F99" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G99" s="52" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H99" s="49" t="s">
         <v>202</v>
@@ -7150,31 +7174,32 @@
         <v>246</v>
       </c>
       <c r="L99" s="46"/>
+      <c r="N99" s="89"/>
       <c r="O99" s="59" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A100" s="79" t="s">
-        <v>486</v>
-      </c>
-      <c r="B100" s="75" t="s">
-        <v>390</v>
+        <v>485</v>
+      </c>
+      <c r="B100" s="61" t="s">
+        <v>391</v>
       </c>
       <c r="C100" s="49" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="D100" s="62" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E100" s="49" t="s">
-        <v>304</v>
+        <v>201</v>
       </c>
       <c r="F100" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="G100" s="97" t="s">
-        <v>532</v>
+      <c r="G100" s="52" t="s">
+        <v>279</v>
       </c>
       <c r="H100" s="49" t="s">
         <v>202</v>
@@ -7183,200 +7208,224 @@
         <v>246</v>
       </c>
       <c r="L100" s="46"/>
+      <c r="O100" s="59" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="101" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A101" s="79" t="s">
-        <v>487</v>
-      </c>
-      <c r="B101" s="100" t="s">
+        <v>486</v>
+      </c>
+      <c r="B101" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="C101" s="90" t="s">
-        <v>496</v>
-      </c>
-      <c r="D101" s="99" t="s">
-        <v>497</v>
-      </c>
-      <c r="E101" s="90" t="s">
-        <v>498</v>
+      <c r="C101" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="E101" s="49" t="s">
+        <v>304</v>
       </c>
       <c r="F101" s="49" t="s">
         <v>204</v>
       </c>
       <c r="G101" s="97" t="s">
+        <v>532</v>
+      </c>
+      <c r="H101" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="I101" s="93" t="s">
+        <v>246</v>
+      </c>
+      <c r="L101" s="46"/>
+    </row>
+    <row r="102" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A102" s="79" t="s">
+        <v>487</v>
+      </c>
+      <c r="B102" s="100" t="s">
+        <v>390</v>
+      </c>
+      <c r="C102" s="90" t="s">
+        <v>496</v>
+      </c>
+      <c r="D102" s="99" t="s">
+        <v>497</v>
+      </c>
+      <c r="E102" s="90" t="s">
+        <v>498</v>
+      </c>
+      <c r="F102" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" s="97" t="s">
         <v>499</v>
       </c>
-      <c r="H101" s="49"/>
-      <c r="I101" s="36" t="s">
+      <c r="H102" s="49"/>
+      <c r="I102" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="J101" s="101" t="s">
+      <c r="J102" s="101" t="s">
         <v>388</v>
       </c>
-      <c r="L101" s="46"/>
-    </row>
-    <row r="102" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A102" s="103" t="s">
+      <c r="L102" s="46"/>
+    </row>
+    <row r="103" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A103" s="103" t="s">
         <v>518</v>
       </c>
-      <c r="B102" s="100" t="s">
+      <c r="B103" s="100" t="s">
         <v>391</v>
       </c>
-      <c r="C102" s="94" t="s">
+      <c r="C103" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="D102" s="96" t="s">
+      <c r="D103" s="96" t="s">
         <v>522</v>
       </c>
-      <c r="E102" s="94" t="s">
+      <c r="E103" s="94" t="s">
         <v>521</v>
-      </c>
-      <c r="F102" s="94" t="s">
-        <v>204</v>
-      </c>
-      <c r="G102" s="97" t="s">
-        <v>520</v>
-      </c>
-      <c r="H102" s="94"/>
-      <c r="I102" s="93" t="s">
-        <v>388</v>
-      </c>
-      <c r="J102" s="101"/>
-      <c r="K102" s="101"/>
-      <c r="L102" s="101"/>
-      <c r="M102" s="114"/>
-      <c r="N102" s="89" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A103" s="105" t="s">
-        <v>500</v>
-      </c>
-      <c r="B103" s="100" t="s">
-        <v>390</v>
-      </c>
-      <c r="C103" s="94" t="s">
-        <v>501</v>
-      </c>
-      <c r="D103" s="96" t="s">
-        <v>502</v>
-      </c>
-      <c r="E103" s="94" t="s">
-        <v>503</v>
       </c>
       <c r="F103" s="94" t="s">
         <v>204</v>
       </c>
       <c r="G103" s="97" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="H103" s="94"/>
       <c r="I103" s="93" t="s">
         <v>388</v>
       </c>
-      <c r="L103" s="46"/>
-    </row>
-    <row r="104" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="J103" s="101"/>
+      <c r="K103" s="101"/>
+      <c r="L103" s="101"/>
+      <c r="M103" s="114" t="s">
+        <v>599</v>
+      </c>
+      <c r="N103" s="89" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A104" s="105" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B104" s="100" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C104" s="94" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="D104" s="96" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E104" s="94" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="F104" s="94" t="s">
         <v>204</v>
       </c>
       <c r="G104" s="97" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H104" s="94"/>
       <c r="I104" s="93" t="s">
         <v>388</v>
       </c>
       <c r="L104" s="46"/>
-      <c r="M104" s="117"/>
-    </row>
-    <row r="105" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A105" s="105" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B105" s="100" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C105" s="94" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D105" s="96" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E105" s="94" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F105" s="94" t="s">
         <v>204</v>
       </c>
       <c r="G105" s="97" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="H105" s="94"/>
       <c r="I105" s="93" t="s">
         <v>388</v>
       </c>
-      <c r="J105" s="101"/>
       <c r="L105" s="46"/>
-      <c r="M105" s="114" t="s">
-        <v>584</v>
-      </c>
-      <c r="N105" s="89" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A106" s="101"/>
-      <c r="B106" s="100"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="96"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="97"/>
+      <c r="M105" s="117"/>
+    </row>
+    <row r="106" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="105" t="s">
+        <v>517</v>
+      </c>
+      <c r="B106" s="100" t="s">
+        <v>391</v>
+      </c>
+      <c r="C106" s="94" t="s">
+        <v>512</v>
+      </c>
+      <c r="D106" s="96" t="s">
+        <v>513</v>
+      </c>
+      <c r="E106" s="94" t="s">
+        <v>515</v>
+      </c>
+      <c r="F106" s="94" t="s">
+        <v>204</v>
+      </c>
+      <c r="G106" s="97" t="s">
+        <v>516</v>
+      </c>
       <c r="H106" s="94"/>
-      <c r="I106" s="93"/>
+      <c r="I106" s="93" t="s">
+        <v>388</v>
+      </c>
       <c r="J106" s="101"/>
       <c r="L106" s="46"/>
-      <c r="M106" s="117"/>
+      <c r="M106" s="114" t="s">
+        <v>576</v>
+      </c>
+      <c r="N106" s="89" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B107" s="39"/>
-      <c r="C107" s="40"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="40"/>
-      <c r="F107" s="40"/>
-      <c r="G107" s="52"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="36"/>
+      <c r="A107" s="101"/>
+      <c r="B107" s="100"/>
+      <c r="C107" s="94"/>
+      <c r="D107" s="96"/>
+      <c r="E107" s="94"/>
+      <c r="F107" s="94"/>
+      <c r="G107" s="97"/>
+      <c r="H107" s="94"/>
+      <c r="I107" s="93"/>
+      <c r="J107" s="101"/>
       <c r="L107" s="46"/>
       <c r="M107" s="117"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B108" s="39"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="37"/>
-      <c r="E108" s="35"/>
+      <c r="C108" s="40"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="40"/>
       <c r="F108" s="40"/>
       <c r="G108" s="52"/>
       <c r="H108" s="40"/>
       <c r="I108" s="36"/>
       <c r="L108" s="46"/>
+      <c r="M108" s="117"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B109" s="39"/>
@@ -7391,21 +7440,20 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B110" s="39"/>
-      <c r="C110" s="40"/>
-      <c r="D110" s="41"/>
+      <c r="C110" s="35"/>
+      <c r="D110" s="37"/>
       <c r="E110" s="35"/>
       <c r="F110" s="40"/>
       <c r="G110" s="52"/>
       <c r="H110" s="40"/>
       <c r="I110" s="36"/>
       <c r="L110" s="46"/>
-      <c r="M110" s="117"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B111" s="39"/>
       <c r="C111" s="40"/>
       <c r="D111" s="41"/>
-      <c r="E111" s="40"/>
+      <c r="E111" s="35"/>
       <c r="F111" s="40"/>
       <c r="G111" s="52"/>
       <c r="H111" s="40"/>
@@ -7451,15 +7499,15 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B115" s="39"/>
-      <c r="C115" s="35"/>
-      <c r="D115" s="37"/>
+      <c r="C115" s="40"/>
+      <c r="D115" s="41"/>
       <c r="E115" s="40"/>
       <c r="F115" s="40"/>
       <c r="G115" s="52"/>
-      <c r="H115" s="35"/>
+      <c r="H115" s="40"/>
       <c r="I115" s="36"/>
       <c r="L115" s="46"/>
-      <c r="M115" s="118"/>
+      <c r="M115" s="117"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B116" s="39"/>
@@ -7487,15 +7535,15 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B118" s="39"/>
-      <c r="C118" s="40"/>
-      <c r="D118" s="41"/>
+      <c r="C118" s="35"/>
+      <c r="D118" s="37"/>
       <c r="E118" s="40"/>
       <c r="F118" s="40"/>
       <c r="G118" s="52"/>
-      <c r="H118" s="40"/>
+      <c r="H118" s="35"/>
       <c r="I118" s="36"/>
       <c r="L118" s="46"/>
-      <c r="M118" s="119"/>
+      <c r="M118" s="118"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B119" s="39"/>
@@ -7507,7 +7555,7 @@
       <c r="H119" s="40"/>
       <c r="I119" s="36"/>
       <c r="L119" s="46"/>
-      <c r="M119" s="117"/>
+      <c r="M119" s="119"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B120" s="39"/>
@@ -7516,9 +7564,10 @@
       <c r="E120" s="40"/>
       <c r="F120" s="40"/>
       <c r="G120" s="52"/>
-      <c r="H120" s="35"/>
+      <c r="H120" s="40"/>
       <c r="I120" s="36"/>
       <c r="L120" s="46"/>
+      <c r="M120" s="117"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B121" s="39"/>
@@ -7527,13 +7576,11 @@
       <c r="E121" s="40"/>
       <c r="F121" s="40"/>
       <c r="G121" s="52"/>
-      <c r="H121" s="40"/>
+      <c r="H121" s="35"/>
       <c r="I121" s="36"/>
       <c r="L121" s="46"/>
-      <c r="M121" s="117"/>
-    </row>
-    <row r="122" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="46"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B122" s="39"/>
       <c r="C122" s="40"/>
       <c r="D122" s="41"/>
@@ -7542,11 +7589,8 @@
       <c r="G122" s="52"/>
       <c r="H122" s="40"/>
       <c r="I122" s="36"/>
-      <c r="J122" s="46"/>
-      <c r="K122" s="46"/>
       <c r="L122" s="46"/>
       <c r="M122" s="117"/>
-      <c r="O122" s="59"/>
     </row>
     <row r="123" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="46"/>
@@ -7564,23 +7608,27 @@
       <c r="M123" s="117"/>
       <c r="O123" s="59"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="46"/>
       <c r="B124" s="39"/>
-      <c r="C124" s="35"/>
-      <c r="D124" s="37"/>
-      <c r="E124" s="35"/>
+      <c r="C124" s="40"/>
+      <c r="D124" s="41"/>
+      <c r="E124" s="40"/>
       <c r="F124" s="40"/>
       <c r="G124" s="52"/>
-      <c r="H124" s="35"/>
+      <c r="H124" s="40"/>
       <c r="I124" s="36"/>
+      <c r="J124" s="46"/>
+      <c r="K124" s="46"/>
       <c r="L124" s="46"/>
-      <c r="M124" s="118"/>
+      <c r="M124" s="117"/>
+      <c r="O124" s="59"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B125" s="39"/>
       <c r="C125" s="35"/>
       <c r="D125" s="37"/>
-      <c r="E125" s="40"/>
+      <c r="E125" s="35"/>
       <c r="F125" s="40"/>
       <c r="G125" s="52"/>
       <c r="H125" s="35"/>
@@ -7601,8 +7649,7 @@
       <c r="M126" s="118"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A127" s="36"/>
-      <c r="B127" s="40"/>
+      <c r="B127" s="39"/>
       <c r="C127" s="35"/>
       <c r="D127" s="37"/>
       <c r="E127" s="40"/>
@@ -7610,36 +7657,38 @@
       <c r="G127" s="52"/>
       <c r="H127" s="35"/>
       <c r="I127" s="36"/>
-      <c r="J127" s="36"/>
-      <c r="K127" s="36"/>
+      <c r="L127" s="46"/>
       <c r="M127" s="118"/>
     </row>
-    <row r="128" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="36"/>
       <c r="B128" s="40"/>
       <c r="C128" s="35"/>
       <c r="D128" s="37"/>
       <c r="E128" s="40"/>
       <c r="F128" s="40"/>
-      <c r="G128" s="38"/>
+      <c r="G128" s="52"/>
       <c r="H128" s="35"/>
       <c r="I128" s="36"/>
       <c r="J128" s="36"/>
       <c r="K128" s="36"/>
       <c r="M128" s="118"/>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B129" s="39"/>
+    <row r="129" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A129" s="36"/>
+      <c r="B129" s="40"/>
       <c r="C129" s="35"/>
       <c r="D129" s="37"/>
-      <c r="E129" s="35"/>
+      <c r="E129" s="40"/>
       <c r="F129" s="40"/>
-      <c r="G129" s="52"/>
+      <c r="G129" s="38"/>
       <c r="H129" s="35"/>
       <c r="I129" s="36"/>
-      <c r="L129" s="46"/>
-    </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J129" s="36"/>
+      <c r="K129" s="36"/>
+      <c r="M129" s="118"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B130" s="39"/>
       <c r="C130" s="35"/>
       <c r="D130" s="37"/>
@@ -7650,7 +7699,7 @@
       <c r="I130" s="36"/>
       <c r="L130" s="46"/>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B131" s="39"/>
       <c r="C131" s="35"/>
       <c r="D131" s="37"/>
@@ -7660,9 +7709,8 @@
       <c r="H131" s="35"/>
       <c r="I131" s="36"/>
       <c r="L131" s="46"/>
-      <c r="M131" s="118"/>
-    </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B132" s="39"/>
       <c r="C132" s="35"/>
       <c r="D132" s="37"/>
@@ -7674,7 +7722,7 @@
       <c r="L132" s="46"/>
       <c r="M132" s="118"/>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B133" s="39"/>
       <c r="C133" s="35"/>
       <c r="D133" s="37"/>
@@ -7684,8 +7732,9 @@
       <c r="H133" s="35"/>
       <c r="I133" s="36"/>
       <c r="L133" s="46"/>
-    </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M133" s="118"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B134" s="39"/>
       <c r="C134" s="35"/>
       <c r="D134" s="37"/>
@@ -7695,9 +7744,8 @@
       <c r="H134" s="35"/>
       <c r="I134" s="36"/>
       <c r="L134" s="46"/>
-      <c r="M134" s="118"/>
-    </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B135" s="39"/>
       <c r="C135" s="35"/>
       <c r="D135" s="37"/>
@@ -7707,8 +7755,9 @@
       <c r="H135" s="35"/>
       <c r="I135" s="36"/>
       <c r="L135" s="46"/>
-    </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M135" s="118"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B136" s="39"/>
       <c r="C136" s="35"/>
       <c r="D136" s="37"/>
@@ -7719,19 +7768,18 @@
       <c r="I136" s="36"/>
       <c r="L136" s="46"/>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B137" s="39"/>
-      <c r="C137" s="40"/>
-      <c r="D137" s="41"/>
-      <c r="E137" s="40"/>
+      <c r="C137" s="35"/>
+      <c r="D137" s="37"/>
+      <c r="E137" s="35"/>
       <c r="F137" s="40"/>
       <c r="G137" s="52"/>
-      <c r="H137" s="40"/>
+      <c r="H137" s="35"/>
       <c r="I137" s="36"/>
       <c r="L137" s="46"/>
-      <c r="M137" s="117"/>
-    </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B138" s="39"/>
       <c r="C138" s="40"/>
       <c r="D138" s="41"/>
@@ -7743,7 +7791,7 @@
       <c r="L138" s="46"/>
       <c r="M138" s="117"/>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B139" s="39"/>
       <c r="C139" s="40"/>
       <c r="D139" s="41"/>
@@ -7755,69 +7803,69 @@
       <c r="L139" s="46"/>
       <c r="M139" s="117"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B140" s="39"/>
-      <c r="C140" s="35"/>
-      <c r="D140" s="37"/>
+      <c r="C140" s="40"/>
+      <c r="D140" s="41"/>
       <c r="E140" s="40"/>
-      <c r="F140" s="35"/>
+      <c r="F140" s="40"/>
       <c r="G140" s="52"/>
-      <c r="H140" s="35"/>
+      <c r="H140" s="40"/>
       <c r="I140" s="36"/>
       <c r="L140" s="46"/>
-    </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M140" s="117"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B141" s="39"/>
-      <c r="C141" s="40"/>
-      <c r="D141" s="41"/>
+      <c r="C141" s="35"/>
+      <c r="D141" s="37"/>
       <c r="E141" s="40"/>
       <c r="F141" s="35"/>
       <c r="G141" s="52"/>
-      <c r="H141" s="40"/>
+      <c r="H141" s="35"/>
       <c r="I141" s="36"/>
       <c r="L141" s="46"/>
-      <c r="M141" s="117"/>
-    </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B142" s="39"/>
-      <c r="C142" s="35"/>
-      <c r="D142" s="37"/>
-      <c r="E142" s="35"/>
+      <c r="C142" s="40"/>
+      <c r="D142" s="41"/>
+      <c r="E142" s="40"/>
       <c r="F142" s="35"/>
       <c r="G142" s="52"/>
-      <c r="H142" s="35"/>
+      <c r="H142" s="40"/>
       <c r="I142" s="36"/>
       <c r="L142" s="46"/>
-      <c r="M142" s="118"/>
-    </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M142" s="117"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B143" s="39"/>
-      <c r="C143" s="40"/>
-      <c r="D143" s="41"/>
-      <c r="E143" s="40"/>
+      <c r="C143" s="35"/>
+      <c r="D143" s="37"/>
+      <c r="E143" s="35"/>
       <c r="F143" s="35"/>
       <c r="G143" s="52"/>
-      <c r="H143" s="40"/>
+      <c r="H143" s="35"/>
       <c r="I143" s="36"/>
       <c r="L143" s="46"/>
-    </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M143" s="118"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B144" s="39"/>
-      <c r="C144" s="47"/>
+      <c r="C144" s="40"/>
       <c r="D144" s="41"/>
-      <c r="E144" s="47"/>
+      <c r="E144" s="40"/>
       <c r="F144" s="35"/>
       <c r="G144" s="52"/>
       <c r="H144" s="40"/>
       <c r="I144" s="36"/>
       <c r="L144" s="46"/>
-      <c r="M144" s="117"/>
     </row>
     <row r="145" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B145" s="39"/>
-      <c r="C145" s="40"/>
+      <c r="C145" s="47"/>
       <c r="D145" s="41"/>
-      <c r="E145" s="40"/>
+      <c r="E145" s="47"/>
       <c r="F145" s="35"/>
       <c r="G145" s="52"/>
       <c r="H145" s="40"/>
@@ -7835,42 +7883,42 @@
       <c r="H146" s="40"/>
       <c r="I146" s="36"/>
       <c r="L146" s="46"/>
+      <c r="M146" s="117"/>
     </row>
     <row r="147" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B147" s="39"/>
-      <c r="C147" s="35"/>
-      <c r="D147" s="37"/>
+      <c r="C147" s="40"/>
+      <c r="D147" s="41"/>
       <c r="E147" s="40"/>
       <c r="F147" s="35"/>
       <c r="G147" s="52"/>
-      <c r="H147" s="35"/>
+      <c r="H147" s="40"/>
       <c r="I147" s="36"/>
       <c r="L147" s="46"/>
-      <c r="M147" s="118"/>
     </row>
     <row r="148" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B148" s="39"/>
-      <c r="C148" s="40"/>
-      <c r="D148" s="41"/>
+      <c r="C148" s="35"/>
+      <c r="D148" s="37"/>
       <c r="E148" s="40"/>
       <c r="F148" s="35"/>
       <c r="G148" s="52"/>
-      <c r="H148" s="40"/>
+      <c r="H148" s="35"/>
       <c r="I148" s="36"/>
       <c r="L148" s="46"/>
-      <c r="M148" s="117"/>
+      <c r="M148" s="118"/>
     </row>
     <row r="149" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B149" s="39"/>
-      <c r="C149" s="35"/>
-      <c r="D149" s="37"/>
-      <c r="E149" s="35"/>
+      <c r="C149" s="40"/>
+      <c r="D149" s="41"/>
+      <c r="E149" s="40"/>
       <c r="F149" s="35"/>
       <c r="G149" s="52"/>
-      <c r="H149" s="35"/>
+      <c r="H149" s="40"/>
       <c r="I149" s="36"/>
       <c r="L149" s="46"/>
-      <c r="M149" s="118"/>
+      <c r="M149" s="117"/>
     </row>
     <row r="150" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B150" s="39"/>
@@ -7886,14 +7934,15 @@
     </row>
     <row r="151" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B151" s="39"/>
-      <c r="C151" s="40"/>
-      <c r="D151" s="41"/>
-      <c r="E151" s="40"/>
+      <c r="C151" s="35"/>
+      <c r="D151" s="37"/>
+      <c r="E151" s="35"/>
       <c r="F151" s="35"/>
       <c r="G151" s="52"/>
-      <c r="H151" s="40"/>
+      <c r="H151" s="35"/>
       <c r="I151" s="36"/>
       <c r="L151" s="46"/>
+      <c r="M151" s="118"/>
     </row>
     <row r="152" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B152" s="39"/>
@@ -7930,26 +7979,26 @@
     </row>
     <row r="155" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B155" s="39"/>
-      <c r="C155" s="35"/>
-      <c r="D155" s="37"/>
-      <c r="E155" s="35"/>
+      <c r="C155" s="40"/>
+      <c r="D155" s="41"/>
+      <c r="E155" s="40"/>
       <c r="F155" s="35"/>
       <c r="G155" s="52"/>
       <c r="H155" s="40"/>
       <c r="I155" s="36"/>
       <c r="L155" s="46"/>
-      <c r="M155" s="118"/>
     </row>
     <row r="156" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B156" s="39"/>
-      <c r="C156" s="40"/>
-      <c r="D156" s="41"/>
+      <c r="C156" s="35"/>
+      <c r="D156" s="37"/>
       <c r="E156" s="35"/>
       <c r="F156" s="35"/>
       <c r="G156" s="52"/>
       <c r="H156" s="40"/>
       <c r="I156" s="36"/>
       <c r="L156" s="46"/>
+      <c r="M156" s="118"/>
     </row>
     <row r="157" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B157" s="39"/>
@@ -7977,7 +8026,7 @@
       <c r="B159" s="39"/>
       <c r="C159" s="40"/>
       <c r="D159" s="41"/>
-      <c r="E159" s="40"/>
+      <c r="E159" s="35"/>
       <c r="F159" s="35"/>
       <c r="G159" s="52"/>
       <c r="H159" s="40"/>
@@ -8016,7 +8065,6 @@
       <c r="H162" s="40"/>
       <c r="I162" s="36"/>
       <c r="L162" s="46"/>
-      <c r="M162" s="117"/>
     </row>
     <row r="163" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B163" s="39"/>
@@ -8028,29 +8076,30 @@
       <c r="H163" s="40"/>
       <c r="I163" s="36"/>
       <c r="L163" s="46"/>
+      <c r="M163" s="117"/>
     </row>
     <row r="164" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B164" s="39"/>
-      <c r="C164" s="35"/>
-      <c r="D164" s="37"/>
-      <c r="E164" s="35"/>
+      <c r="C164" s="40"/>
+      <c r="D164" s="41"/>
+      <c r="E164" s="40"/>
       <c r="F164" s="35"/>
       <c r="G164" s="52"/>
-      <c r="H164" s="35"/>
+      <c r="H164" s="40"/>
       <c r="I164" s="36"/>
       <c r="L164" s="46"/>
-      <c r="M164" s="118"/>
     </row>
     <row r="165" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B165" s="39"/>
-      <c r="C165" s="40"/>
-      <c r="D165" s="41"/>
-      <c r="E165" s="40"/>
+      <c r="C165" s="35"/>
+      <c r="D165" s="37"/>
+      <c r="E165" s="35"/>
       <c r="F165" s="35"/>
       <c r="G165" s="52"/>
-      <c r="H165" s="40"/>
+      <c r="H165" s="35"/>
       <c r="I165" s="36"/>
       <c r="L165" s="46"/>
+      <c r="M165" s="118"/>
     </row>
     <row r="166" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B166" s="39"/>
@@ -8062,31 +8111,30 @@
       <c r="H166" s="40"/>
       <c r="I166" s="36"/>
       <c r="L166" s="46"/>
-      <c r="M166" s="117"/>
     </row>
     <row r="167" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B167" s="39"/>
-      <c r="C167" s="35"/>
-      <c r="D167" s="37"/>
-      <c r="E167" s="35"/>
+      <c r="C167" s="40"/>
+      <c r="D167" s="41"/>
+      <c r="E167" s="40"/>
       <c r="F167" s="35"/>
       <c r="G167" s="52"/>
-      <c r="H167" s="35"/>
+      <c r="H167" s="40"/>
       <c r="I167" s="36"/>
       <c r="L167" s="46"/>
-      <c r="M167" s="118"/>
+      <c r="M167" s="117"/>
     </row>
     <row r="168" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B168" s="39"/>
-      <c r="C168" s="40"/>
-      <c r="D168" s="41"/>
-      <c r="E168" s="40"/>
+      <c r="C168" s="35"/>
+      <c r="D168" s="37"/>
+      <c r="E168" s="35"/>
       <c r="F168" s="35"/>
       <c r="G168" s="52"/>
-      <c r="H168" s="40"/>
+      <c r="H168" s="35"/>
       <c r="I168" s="36"/>
       <c r="L168" s="46"/>
-      <c r="M168" s="117"/>
+      <c r="M168" s="118"/>
     </row>
     <row r="169" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B169" s="39"/>
@@ -8110,6 +8158,7 @@
       <c r="H170" s="40"/>
       <c r="I170" s="36"/>
       <c r="L170" s="46"/>
+      <c r="M170" s="117"/>
     </row>
     <row r="171" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B171" s="39"/>
@@ -8198,7 +8247,6 @@
       <c r="H178" s="40"/>
       <c r="I178" s="36"/>
       <c r="L178" s="46"/>
-      <c r="M178" s="117"/>
     </row>
     <row r="179" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B179" s="39"/>
@@ -8222,6 +8270,7 @@
       <c r="H180" s="40"/>
       <c r="I180" s="36"/>
       <c r="L180" s="46"/>
+      <c r="M180" s="117"/>
     </row>
     <row r="181" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B181" s="39"/>
@@ -8244,7 +8293,6 @@
       <c r="H182" s="40"/>
       <c r="I182" s="36"/>
       <c r="L182" s="46"/>
-      <c r="M182" s="117"/>
     </row>
     <row r="183" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B183" s="39"/>
@@ -8284,27 +8332,27 @@
     </row>
     <row r="186" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B186" s="39"/>
-      <c r="C186" s="35"/>
-      <c r="D186" s="37"/>
-      <c r="E186" s="35"/>
+      <c r="C186" s="40"/>
+      <c r="D186" s="41"/>
+      <c r="E186" s="40"/>
       <c r="F186" s="35"/>
       <c r="G186" s="52"/>
-      <c r="H186" s="35"/>
+      <c r="H186" s="40"/>
       <c r="I186" s="36"/>
       <c r="L186" s="46"/>
-      <c r="M186" s="118"/>
+      <c r="M186" s="117"/>
     </row>
     <row r="187" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B187" s="39"/>
-      <c r="C187" s="40"/>
-      <c r="D187" s="41"/>
-      <c r="E187" s="40"/>
+      <c r="C187" s="35"/>
+      <c r="D187" s="37"/>
+      <c r="E187" s="35"/>
       <c r="F187" s="35"/>
       <c r="G187" s="52"/>
-      <c r="H187" s="40"/>
+      <c r="H187" s="35"/>
       <c r="I187" s="36"/>
       <c r="L187" s="46"/>
-      <c r="M187" s="117"/>
+      <c r="M187" s="118"/>
     </row>
     <row r="188" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B188" s="39"/>
@@ -8340,6 +8388,7 @@
       <c r="H190" s="40"/>
       <c r="I190" s="36"/>
       <c r="L190" s="46"/>
+      <c r="M190" s="117"/>
     </row>
     <row r="191" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B191" s="39"/>
@@ -8362,7 +8411,6 @@
       <c r="H192" s="40"/>
       <c r="I192" s="36"/>
       <c r="L192" s="46"/>
-      <c r="M192" s="117"/>
     </row>
     <row r="193" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B193" s="39"/>
@@ -8374,6 +8422,7 @@
       <c r="H193" s="40"/>
       <c r="I193" s="36"/>
       <c r="L193" s="46"/>
+      <c r="M193" s="117"/>
     </row>
     <row r="194" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B194" s="39"/>
@@ -8410,49 +8459,49 @@
     </row>
     <row r="197" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B197" s="39"/>
-      <c r="C197" s="35"/>
-      <c r="D197" s="37"/>
-      <c r="E197" s="35"/>
+      <c r="C197" s="40"/>
+      <c r="D197" s="41"/>
+      <c r="E197" s="40"/>
       <c r="F197" s="35"/>
       <c r="G197" s="52"/>
-      <c r="H197" s="35"/>
+      <c r="H197" s="40"/>
       <c r="I197" s="36"/>
       <c r="L197" s="46"/>
-      <c r="M197" s="118"/>
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B198" s="39"/>
-      <c r="C198" s="40"/>
-      <c r="D198" s="41"/>
-      <c r="E198" s="40"/>
+      <c r="C198" s="35"/>
+      <c r="D198" s="37"/>
+      <c r="E198" s="35"/>
       <c r="F198" s="35"/>
       <c r="G198" s="52"/>
-      <c r="H198" s="40"/>
+      <c r="H198" s="35"/>
       <c r="I198" s="36"/>
       <c r="L198" s="46"/>
+      <c r="M198" s="118"/>
     </row>
     <row r="199" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B199" s="39"/>
-      <c r="C199" s="35"/>
-      <c r="D199" s="37"/>
-      <c r="E199" s="35"/>
+      <c r="C199" s="40"/>
+      <c r="D199" s="41"/>
+      <c r="E199" s="40"/>
       <c r="F199" s="35"/>
       <c r="G199" s="52"/>
-      <c r="H199" s="35"/>
+      <c r="H199" s="40"/>
       <c r="I199" s="36"/>
       <c r="L199" s="46"/>
-      <c r="M199" s="118"/>
     </row>
     <row r="200" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B200" s="39"/>
-      <c r="C200" s="40"/>
-      <c r="D200" s="41"/>
-      <c r="E200" s="40"/>
+      <c r="C200" s="35"/>
+      <c r="D200" s="37"/>
+      <c r="E200" s="35"/>
       <c r="F200" s="35"/>
       <c r="G200" s="52"/>
-      <c r="H200" s="40"/>
+      <c r="H200" s="35"/>
       <c r="I200" s="36"/>
       <c r="L200" s="46"/>
+      <c r="M200" s="118"/>
     </row>
     <row r="201" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B201" s="39"/>
@@ -8464,7 +8513,6 @@
       <c r="H201" s="40"/>
       <c r="I201" s="36"/>
       <c r="L201" s="46"/>
-      <c r="M201" s="117"/>
     </row>
     <row r="202" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B202" s="39"/>
@@ -8476,6 +8524,7 @@
       <c r="H202" s="40"/>
       <c r="I202" s="36"/>
       <c r="L202" s="46"/>
+      <c r="M202" s="117"/>
     </row>
     <row r="203" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B203" s="39"/>
@@ -8487,7 +8536,6 @@
       <c r="H203" s="40"/>
       <c r="I203" s="36"/>
       <c r="L203" s="46"/>
-      <c r="M203" s="117"/>
     </row>
     <row r="204" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B204" s="39"/>
@@ -8511,6 +8559,7 @@
       <c r="H205" s="40"/>
       <c r="I205" s="36"/>
       <c r="L205" s="46"/>
+      <c r="M205" s="117"/>
     </row>
     <row r="206" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B206" s="39"/>
@@ -8533,30 +8582,30 @@
       <c r="H207" s="40"/>
       <c r="I207" s="36"/>
       <c r="L207" s="46"/>
-      <c r="M207" s="117"/>
     </row>
     <row r="208" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B208" s="39"/>
-      <c r="C208" s="35"/>
-      <c r="D208" s="37"/>
-      <c r="E208" s="35"/>
+      <c r="C208" s="40"/>
+      <c r="D208" s="41"/>
+      <c r="E208" s="40"/>
       <c r="F208" s="35"/>
       <c r="G208" s="52"/>
-      <c r="H208" s="35"/>
+      <c r="H208" s="40"/>
       <c r="I208" s="36"/>
       <c r="L208" s="46"/>
-      <c r="M208" s="118"/>
+      <c r="M208" s="117"/>
     </row>
     <row r="209" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B209" s="39"/>
-      <c r="C209" s="40"/>
-      <c r="D209" s="41"/>
-      <c r="E209" s="40"/>
+      <c r="C209" s="35"/>
+      <c r="D209" s="37"/>
+      <c r="E209" s="35"/>
       <c r="F209" s="35"/>
       <c r="G209" s="52"/>
-      <c r="H209" s="40"/>
+      <c r="H209" s="35"/>
       <c r="I209" s="36"/>
       <c r="L209" s="46"/>
+      <c r="M209" s="118"/>
     </row>
     <row r="210" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B210" s="39"/>
@@ -8568,7 +8617,6 @@
       <c r="H210" s="40"/>
       <c r="I210" s="36"/>
       <c r="L210" s="46"/>
-      <c r="M210" s="117"/>
     </row>
     <row r="211" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B211" s="39"/>
@@ -8608,27 +8656,27 @@
     </row>
     <row r="214" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B214" s="39"/>
-      <c r="C214" s="35"/>
-      <c r="D214" s="37"/>
+      <c r="C214" s="40"/>
+      <c r="D214" s="41"/>
       <c r="E214" s="40"/>
       <c r="F214" s="35"/>
       <c r="G214" s="52"/>
-      <c r="H214" s="35"/>
+      <c r="H214" s="40"/>
       <c r="I214" s="36"/>
       <c r="L214" s="46"/>
-      <c r="M214" s="118"/>
+      <c r="M214" s="117"/>
     </row>
     <row r="215" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B215" s="39"/>
-      <c r="C215" s="40"/>
-      <c r="D215" s="41"/>
+      <c r="C215" s="35"/>
+      <c r="D215" s="37"/>
       <c r="E215" s="40"/>
       <c r="F215" s="35"/>
       <c r="G215" s="52"/>
-      <c r="H215" s="40"/>
+      <c r="H215" s="35"/>
       <c r="I215" s="36"/>
       <c r="L215" s="46"/>
-      <c r="M215" s="117"/>
+      <c r="M215" s="118"/>
     </row>
     <row r="216" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B216" s="39"/>
@@ -8656,39 +8704,39 @@
     </row>
     <row r="218" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B218" s="39"/>
-      <c r="C218" s="35"/>
-      <c r="D218" s="37"/>
+      <c r="C218" s="40"/>
+      <c r="D218" s="41"/>
       <c r="E218" s="40"/>
       <c r="F218" s="35"/>
       <c r="G218" s="52"/>
-      <c r="H218" s="35"/>
+      <c r="H218" s="40"/>
       <c r="I218" s="36"/>
       <c r="L218" s="46"/>
-      <c r="M218" s="118"/>
+      <c r="M218" s="117"/>
     </row>
     <row r="219" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B219" s="39"/>
-      <c r="C219" s="40"/>
-      <c r="D219" s="41"/>
+      <c r="C219" s="35"/>
+      <c r="D219" s="37"/>
       <c r="E219" s="40"/>
       <c r="F219" s="35"/>
       <c r="G219" s="52"/>
-      <c r="H219" s="40"/>
+      <c r="H219" s="35"/>
       <c r="I219" s="36"/>
       <c r="L219" s="46"/>
-      <c r="M219" s="117"/>
+      <c r="M219" s="118"/>
     </row>
     <row r="220" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B220" s="39"/>
-      <c r="C220" s="35"/>
-      <c r="D220" s="37"/>
-      <c r="E220" s="35"/>
+      <c r="C220" s="40"/>
+      <c r="D220" s="41"/>
+      <c r="E220" s="40"/>
       <c r="F220" s="35"/>
       <c r="G220" s="52"/>
-      <c r="H220" s="35"/>
+      <c r="H220" s="40"/>
       <c r="I220" s="36"/>
       <c r="L220" s="46"/>
-      <c r="M220" s="118"/>
+      <c r="M220" s="117"/>
     </row>
     <row r="221" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B221" s="39"/>
@@ -8704,15 +8752,15 @@
     </row>
     <row r="222" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B222" s="39"/>
-      <c r="C222" s="40"/>
-      <c r="D222" s="41"/>
-      <c r="E222" s="40"/>
+      <c r="C222" s="35"/>
+      <c r="D222" s="37"/>
+      <c r="E222" s="35"/>
       <c r="F222" s="35"/>
       <c r="G222" s="52"/>
       <c r="H222" s="35"/>
       <c r="I222" s="36"/>
       <c r="L222" s="46"/>
-      <c r="M222" s="117"/>
+      <c r="M222" s="118"/>
     </row>
     <row r="223" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B223" s="39"/>
@@ -8745,7 +8793,7 @@
       <c r="E225" s="40"/>
       <c r="F225" s="35"/>
       <c r="G225" s="52"/>
-      <c r="H225" s="40"/>
+      <c r="H225" s="35"/>
       <c r="I225" s="36"/>
       <c r="L225" s="46"/>
       <c r="M225" s="117"/>
@@ -8788,15 +8836,15 @@
     </row>
     <row r="229" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B229" s="39"/>
-      <c r="C229" s="35"/>
-      <c r="D229" s="37"/>
-      <c r="E229" s="35"/>
+      <c r="C229" s="40"/>
+      <c r="D229" s="41"/>
+      <c r="E229" s="40"/>
       <c r="F229" s="35"/>
       <c r="G229" s="52"/>
-      <c r="H229" s="35"/>
+      <c r="H229" s="40"/>
       <c r="I229" s="36"/>
       <c r="L229" s="46"/>
-      <c r="M229" s="118"/>
+      <c r="M229" s="117"/>
     </row>
     <row r="230" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B230" s="39"/>
@@ -8832,18 +8880,19 @@
       <c r="H232" s="35"/>
       <c r="I232" s="36"/>
       <c r="L232" s="46"/>
-      <c r="M232" s="119"/>
+      <c r="M232" s="118"/>
     </row>
     <row r="233" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B233" s="39"/>
-      <c r="C233" s="40"/>
+      <c r="C233" s="35"/>
       <c r="D233" s="37"/>
-      <c r="E233" s="40"/>
+      <c r="E233" s="35"/>
       <c r="F233" s="35"/>
       <c r="G233" s="52"/>
-      <c r="H233" s="40"/>
+      <c r="H233" s="35"/>
       <c r="I233" s="36"/>
       <c r="L233" s="46"/>
+      <c r="M233" s="119"/>
     </row>
     <row r="234" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B234" s="39"/>
@@ -8859,14 +8908,13 @@
     <row r="235" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B235" s="39"/>
       <c r="C235" s="40"/>
-      <c r="D235" s="41"/>
+      <c r="D235" s="37"/>
       <c r="E235" s="40"/>
       <c r="F235" s="35"/>
       <c r="G235" s="52"/>
       <c r="H235" s="40"/>
       <c r="I235" s="36"/>
       <c r="L235" s="46"/>
-      <c r="M235" s="117"/>
     </row>
     <row r="236" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B236" s="39"/>
@@ -8930,19 +8978,19 @@
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B241" s="39"/>
-      <c r="C241" s="35"/>
-      <c r="D241" s="37"/>
+      <c r="C241" s="40"/>
+      <c r="D241" s="41"/>
       <c r="E241" s="40"/>
       <c r="F241" s="35"/>
       <c r="G241" s="52"/>
-      <c r="H241" s="35"/>
+      <c r="H241" s="40"/>
       <c r="I241" s="36"/>
       <c r="L241" s="46"/>
-      <c r="M241" s="119"/>
+      <c r="M241" s="117"/>
     </row>
     <row r="242" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B242" s="39"/>
-      <c r="C242" s="40"/>
+      <c r="C242" s="35"/>
       <c r="D242" s="37"/>
       <c r="E242" s="40"/>
       <c r="F242" s="35"/>
@@ -8950,7 +8998,7 @@
       <c r="H242" s="35"/>
       <c r="I242" s="36"/>
       <c r="L242" s="46"/>
-      <c r="M242" s="118"/>
+      <c r="M242" s="119"/>
     </row>
     <row r="243" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B243" s="39"/>
@@ -8959,14 +9007,15 @@
       <c r="E243" s="40"/>
       <c r="F243" s="35"/>
       <c r="G243" s="52"/>
-      <c r="H243" s="40"/>
+      <c r="H243" s="35"/>
       <c r="I243" s="36"/>
       <c r="L243" s="46"/>
+      <c r="M243" s="118"/>
     </row>
     <row r="244" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B244" s="39"/>
       <c r="C244" s="40"/>
-      <c r="D244" s="41"/>
+      <c r="D244" s="37"/>
       <c r="E244" s="40"/>
       <c r="F244" s="35"/>
       <c r="G244" s="52"/>
@@ -8984,14 +9033,13 @@
       <c r="H245" s="40"/>
       <c r="I245" s="36"/>
       <c r="L245" s="46"/>
-      <c r="M245" s="117"/>
     </row>
     <row r="246" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B246" s="39"/>
       <c r="C246" s="40"/>
       <c r="D246" s="41"/>
       <c r="E246" s="40"/>
-      <c r="F246" s="40"/>
+      <c r="F246" s="35"/>
       <c r="G246" s="52"/>
       <c r="H246" s="40"/>
       <c r="I246" s="36"/>
@@ -9003,7 +9051,7 @@
       <c r="C247" s="40"/>
       <c r="D247" s="41"/>
       <c r="E247" s="40"/>
-      <c r="F247" s="35"/>
+      <c r="F247" s="40"/>
       <c r="G247" s="52"/>
       <c r="H247" s="40"/>
       <c r="I247" s="36"/>
@@ -9072,38 +9120,39 @@
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B253" s="39"/>
-      <c r="C253" s="35"/>
-      <c r="D253" s="37"/>
+      <c r="C253" s="40"/>
+      <c r="D253" s="41"/>
       <c r="E253" s="40"/>
       <c r="F253" s="35"/>
       <c r="G253" s="52"/>
       <c r="H253" s="40"/>
       <c r="I253" s="36"/>
       <c r="L253" s="46"/>
-      <c r="M253" s="119"/>
+      <c r="M253" s="117"/>
     </row>
     <row r="254" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B254" s="39"/>
       <c r="C254" s="35"/>
       <c r="D254" s="37"/>
-      <c r="E254" s="35"/>
+      <c r="E254" s="40"/>
       <c r="F254" s="35"/>
       <c r="G254" s="52"/>
       <c r="H254" s="40"/>
       <c r="I254" s="36"/>
       <c r="L254" s="46"/>
-      <c r="M254" s="118"/>
+      <c r="M254" s="119"/>
     </row>
     <row r="255" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B255" s="39"/>
-      <c r="C255" s="40"/>
+      <c r="C255" s="35"/>
       <c r="D255" s="37"/>
-      <c r="E255" s="40"/>
+      <c r="E255" s="35"/>
       <c r="F255" s="35"/>
       <c r="G255" s="52"/>
       <c r="H255" s="40"/>
       <c r="I255" s="36"/>
       <c r="L255" s="46"/>
+      <c r="M255" s="118"/>
     </row>
     <row r="256" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B256" s="39"/>
@@ -9119,7 +9168,7 @@
     <row r="257" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B257" s="39"/>
       <c r="C257" s="40"/>
-      <c r="D257" s="41"/>
+      <c r="D257" s="37"/>
       <c r="E257" s="40"/>
       <c r="F257" s="35"/>
       <c r="G257" s="52"/>
@@ -9137,7 +9186,6 @@
       <c r="H258" s="40"/>
       <c r="I258" s="36"/>
       <c r="L258" s="46"/>
-      <c r="M258" s="117"/>
     </row>
     <row r="259" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B259" s="39"/>
@@ -9153,27 +9201,27 @@
     </row>
     <row r="260" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B260" s="39"/>
-      <c r="C260" s="35"/>
-      <c r="D260" s="37"/>
+      <c r="C260" s="40"/>
+      <c r="D260" s="41"/>
       <c r="E260" s="40"/>
       <c r="F260" s="35"/>
       <c r="G260" s="52"/>
       <c r="H260" s="40"/>
       <c r="I260" s="36"/>
       <c r="L260" s="46"/>
-      <c r="M260" s="118"/>
+      <c r="M260" s="117"/>
     </row>
     <row r="261" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B261" s="39"/>
-      <c r="C261" s="40"/>
-      <c r="D261" s="41"/>
+      <c r="C261" s="35"/>
+      <c r="D261" s="37"/>
       <c r="E261" s="40"/>
       <c r="F261" s="35"/>
       <c r="G261" s="52"/>
       <c r="H261" s="40"/>
       <c r="I261" s="36"/>
       <c r="L261" s="46"/>
-      <c r="M261" s="117"/>
+      <c r="M261" s="118"/>
     </row>
     <row r="262" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B262" s="39"/>
@@ -9257,23 +9305,23 @@
       <c r="H268" s="40"/>
       <c r="I268" s="36"/>
       <c r="L268" s="46"/>
-      <c r="M268" s="119"/>
+      <c r="M268" s="117"/>
     </row>
     <row r="269" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B269" s="39"/>
-      <c r="C269" s="35"/>
-      <c r="D269" s="37"/>
+      <c r="C269" s="40"/>
+      <c r="D269" s="41"/>
       <c r="E269" s="40"/>
       <c r="F269" s="35"/>
       <c r="G269" s="52"/>
       <c r="H269" s="40"/>
       <c r="I269" s="36"/>
       <c r="L269" s="46"/>
-      <c r="M269" s="118"/>
+      <c r="M269" s="119"/>
     </row>
     <row r="270" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B270" s="39"/>
-      <c r="C270" s="40"/>
+      <c r="C270" s="35"/>
       <c r="D270" s="37"/>
       <c r="E270" s="40"/>
       <c r="F270" s="35"/>
@@ -9281,6 +9329,7 @@
       <c r="H270" s="40"/>
       <c r="I270" s="36"/>
       <c r="L270" s="46"/>
+      <c r="M270" s="118"/>
     </row>
     <row r="271" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B271" s="39"/>
@@ -9307,7 +9356,7 @@
     <row r="273" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B273" s="39"/>
       <c r="C273" s="40"/>
-      <c r="D273" s="41"/>
+      <c r="D273" s="37"/>
       <c r="E273" s="40"/>
       <c r="F273" s="35"/>
       <c r="G273" s="52"/>
@@ -9318,7 +9367,7 @@
     <row r="274" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B274" s="39"/>
       <c r="C274" s="40"/>
-      <c r="D274" s="37"/>
+      <c r="D274" s="41"/>
       <c r="E274" s="40"/>
       <c r="F274" s="35"/>
       <c r="G274" s="52"/>
@@ -9329,14 +9378,13 @@
     <row r="275" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B275" s="39"/>
       <c r="C275" s="40"/>
-      <c r="D275" s="41"/>
+      <c r="D275" s="37"/>
       <c r="E275" s="40"/>
       <c r="F275" s="35"/>
       <c r="G275" s="52"/>
       <c r="H275" s="40"/>
       <c r="I275" s="36"/>
       <c r="L275" s="46"/>
-      <c r="M275" s="117"/>
     </row>
     <row r="276" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B276" s="39"/>
@@ -9365,13 +9413,14 @@
     <row r="278" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B278" s="39"/>
       <c r="C278" s="40"/>
-      <c r="D278" s="37"/>
+      <c r="D278" s="41"/>
       <c r="E278" s="40"/>
       <c r="F278" s="35"/>
       <c r="G278" s="52"/>
       <c r="H278" s="40"/>
       <c r="I278" s="36"/>
       <c r="L278" s="46"/>
+      <c r="M278" s="117"/>
     </row>
     <row r="279" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B279" s="39"/>
@@ -9386,7 +9435,7 @@
     </row>
     <row r="280" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B280" s="39"/>
-      <c r="C280" s="35"/>
+      <c r="C280" s="40"/>
       <c r="D280" s="37"/>
       <c r="E280" s="40"/>
       <c r="F280" s="35"/>
@@ -9394,54 +9443,53 @@
       <c r="H280" s="40"/>
       <c r="I280" s="36"/>
       <c r="L280" s="46"/>
-      <c r="M280" s="119"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B281" s="39"/>
-      <c r="C281" s="40"/>
-      <c r="D281" s="41"/>
+      <c r="C281" s="35"/>
+      <c r="D281" s="37"/>
       <c r="E281" s="40"/>
       <c r="F281" s="35"/>
       <c r="G281" s="52"/>
       <c r="H281" s="40"/>
       <c r="I281" s="36"/>
       <c r="L281" s="46"/>
-      <c r="M281" s="117"/>
+      <c r="M281" s="119"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B282" s="39"/>
       <c r="C282" s="40"/>
-      <c r="D282" s="37"/>
+      <c r="D282" s="41"/>
       <c r="E282" s="40"/>
       <c r="F282" s="35"/>
       <c r="G282" s="52"/>
       <c r="H282" s="40"/>
       <c r="I282" s="36"/>
       <c r="L282" s="46"/>
+      <c r="M282" s="117"/>
     </row>
     <row r="283" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B283" s="39"/>
       <c r="C283" s="40"/>
-      <c r="D283" s="41"/>
+      <c r="D283" s="37"/>
       <c r="E283" s="40"/>
       <c r="F283" s="35"/>
       <c r="G283" s="52"/>
       <c r="H283" s="40"/>
       <c r="I283" s="36"/>
       <c r="L283" s="46"/>
-      <c r="M283" s="117"/>
     </row>
     <row r="284" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B284" s="39"/>
-      <c r="C284" s="35"/>
-      <c r="D284" s="37"/>
-      <c r="E284" s="35"/>
+      <c r="C284" s="40"/>
+      <c r="D284" s="41"/>
+      <c r="E284" s="40"/>
       <c r="F284" s="35"/>
       <c r="G284" s="52"/>
       <c r="H284" s="40"/>
       <c r="I284" s="36"/>
       <c r="L284" s="46"/>
-      <c r="M284" s="118"/>
+      <c r="M284" s="117"/>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B285" s="39"/>
@@ -9469,26 +9517,26 @@
     </row>
     <row r="287" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B287" s="39"/>
-      <c r="C287" s="40"/>
+      <c r="C287" s="35"/>
       <c r="D287" s="37"/>
-      <c r="E287" s="40"/>
+      <c r="E287" s="35"/>
       <c r="F287" s="35"/>
       <c r="G287" s="52"/>
       <c r="H287" s="40"/>
       <c r="I287" s="36"/>
       <c r="L287" s="46"/>
+      <c r="M287" s="118"/>
     </row>
     <row r="288" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B288" s="39"/>
       <c r="C288" s="40"/>
-      <c r="D288" s="41"/>
+      <c r="D288" s="37"/>
       <c r="E288" s="40"/>
       <c r="F288" s="35"/>
       <c r="G288" s="52"/>
       <c r="H288" s="40"/>
       <c r="I288" s="36"/>
       <c r="L288" s="46"/>
-      <c r="M288" s="117"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B289" s="39"/>
@@ -9528,15 +9576,15 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B292" s="39"/>
-      <c r="C292" s="35"/>
-      <c r="D292" s="37"/>
-      <c r="E292" s="35"/>
+      <c r="C292" s="40"/>
+      <c r="D292" s="41"/>
+      <c r="E292" s="40"/>
       <c r="F292" s="35"/>
       <c r="G292" s="52"/>
       <c r="H292" s="40"/>
       <c r="I292" s="36"/>
       <c r="L292" s="46"/>
-      <c r="M292" s="118"/>
+      <c r="M292" s="117"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B293" s="39"/>
@@ -9552,15 +9600,15 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B294" s="39"/>
-      <c r="C294" s="40"/>
-      <c r="D294" s="41"/>
-      <c r="E294" s="40"/>
+      <c r="C294" s="35"/>
+      <c r="D294" s="37"/>
+      <c r="E294" s="35"/>
       <c r="F294" s="35"/>
       <c r="G294" s="52"/>
       <c r="H294" s="40"/>
       <c r="I294" s="36"/>
       <c r="L294" s="46"/>
-      <c r="M294" s="117"/>
+      <c r="M294" s="118"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B295" s="39"/>
@@ -9625,18 +9673,19 @@
     <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B300" s="39"/>
       <c r="C300" s="40"/>
-      <c r="D300" s="37"/>
+      <c r="D300" s="41"/>
       <c r="E300" s="40"/>
       <c r="F300" s="35"/>
       <c r="G300" s="52"/>
       <c r="H300" s="40"/>
       <c r="I300" s="36"/>
       <c r="L300" s="46"/>
+      <c r="M300" s="117"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B301" s="39"/>
       <c r="C301" s="40"/>
-      <c r="D301" s="41"/>
+      <c r="D301" s="37"/>
       <c r="E301" s="40"/>
       <c r="F301" s="35"/>
       <c r="G301" s="52"/>
@@ -9644,31 +9693,30 @@
       <c r="I301" s="36"/>
       <c r="L301" s="46"/>
     </row>
-    <row r="302" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A302" s="36"/>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B302" s="39"/>
-      <c r="C302" s="43"/>
-      <c r="D302" s="44"/>
-      <c r="E302" s="43"/>
-      <c r="F302" s="40"/>
+      <c r="C302" s="40"/>
+      <c r="D302" s="41"/>
+      <c r="E302" s="40"/>
+      <c r="F302" s="35"/>
       <c r="G302" s="52"/>
-      <c r="H302" s="45"/>
+      <c r="H302" s="40"/>
       <c r="I302" s="36"/>
-      <c r="J302" s="36"/>
-      <c r="K302" s="36"/>
-      <c r="N302" s="42"/>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L302" s="46"/>
+    </row>
+    <row r="303" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+      <c r="A303" s="36"/>
       <c r="B303" s="39"/>
-      <c r="C303" s="40"/>
-      <c r="D303" s="41"/>
-      <c r="E303" s="40"/>
-      <c r="F303" s="35"/>
+      <c r="C303" s="43"/>
+      <c r="D303" s="44"/>
+      <c r="E303" s="43"/>
+      <c r="F303" s="40"/>
       <c r="G303" s="52"/>
-      <c r="H303" s="40"/>
+      <c r="H303" s="45"/>
       <c r="I303" s="36"/>
-      <c r="L303" s="46"/>
-      <c r="M303" s="117"/>
+      <c r="J303" s="36"/>
+      <c r="K303" s="36"/>
+      <c r="N303" s="42"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B304" s="39"/>
@@ -9708,27 +9756,27 @@
     </row>
     <row r="307" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B307" s="39"/>
-      <c r="C307" s="35"/>
-      <c r="D307" s="37"/>
+      <c r="C307" s="40"/>
+      <c r="D307" s="41"/>
       <c r="E307" s="40"/>
       <c r="F307" s="35"/>
       <c r="G307" s="52"/>
-      <c r="H307" s="35"/>
+      <c r="H307" s="40"/>
       <c r="I307" s="36"/>
       <c r="L307" s="46"/>
-      <c r="M307" s="118"/>
+      <c r="M307" s="117"/>
     </row>
     <row r="308" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B308" s="39"/>
-      <c r="C308" s="40"/>
-      <c r="D308" s="41"/>
+      <c r="C308" s="35"/>
+      <c r="D308" s="37"/>
       <c r="E308" s="40"/>
       <c r="F308" s="35"/>
       <c r="G308" s="52"/>
-      <c r="H308" s="40"/>
+      <c r="H308" s="35"/>
       <c r="I308" s="36"/>
       <c r="L308" s="46"/>
-      <c r="M308" s="117"/>
+      <c r="M308" s="118"/>
     </row>
     <row r="309" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B309" s="39"/>
@@ -9740,6 +9788,7 @@
       <c r="H309" s="40"/>
       <c r="I309" s="36"/>
       <c r="L309" s="46"/>
+      <c r="M309" s="117"/>
     </row>
     <row r="310" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B310" s="39"/>
@@ -9751,7 +9800,6 @@
       <c r="H310" s="40"/>
       <c r="I310" s="36"/>
       <c r="L310" s="46"/>
-      <c r="M310" s="117"/>
     </row>
     <row r="311" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B311" s="39"/>
@@ -9823,6 +9871,7 @@
       <c r="H316" s="40"/>
       <c r="I316" s="36"/>
       <c r="L316" s="46"/>
+      <c r="M316" s="117"/>
     </row>
     <row r="317" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B317" s="39"/>
@@ -9834,7 +9883,6 @@
       <c r="H317" s="40"/>
       <c r="I317" s="36"/>
       <c r="L317" s="46"/>
-      <c r="M317" s="117"/>
     </row>
     <row r="318" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B318" s="39"/>
@@ -9870,6 +9918,7 @@
       <c r="H320" s="40"/>
       <c r="I320" s="36"/>
       <c r="L320" s="46"/>
+      <c r="M320" s="117"/>
     </row>
     <row r="321" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B321" s="39"/>
@@ -9925,7 +9974,6 @@
       <c r="H325" s="40"/>
       <c r="I325" s="36"/>
       <c r="L325" s="46"/>
-      <c r="M325" s="117"/>
     </row>
     <row r="326" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B326" s="39"/>
@@ -9937,6 +9985,7 @@
       <c r="H326" s="40"/>
       <c r="I326" s="36"/>
       <c r="L326" s="46"/>
+      <c r="M326" s="117"/>
     </row>
     <row r="327" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B327" s="39"/>
@@ -9948,7 +9997,6 @@
       <c r="H327" s="40"/>
       <c r="I327" s="36"/>
       <c r="L327" s="46"/>
-      <c r="M327" s="117"/>
     </row>
     <row r="328" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B328" s="39"/>
@@ -9969,10 +10017,10 @@
       <c r="E329" s="40"/>
       <c r="F329" s="35"/>
       <c r="G329" s="52"/>
-      <c r="H329" s="35"/>
+      <c r="H329" s="40"/>
       <c r="I329" s="36"/>
       <c r="L329" s="46"/>
-      <c r="M329" s="120"/>
+      <c r="M329" s="117"/>
     </row>
     <row r="330" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B330" s="39"/>
@@ -9981,13 +10029,14 @@
       <c r="E330" s="40"/>
       <c r="F330" s="35"/>
       <c r="G330" s="52"/>
-      <c r="H330" s="40"/>
+      <c r="H330" s="35"/>
       <c r="I330" s="36"/>
       <c r="L330" s="46"/>
+      <c r="M330" s="120"/>
     </row>
     <row r="331" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B331" s="39"/>
-      <c r="C331" s="39"/>
+      <c r="C331" s="40"/>
       <c r="D331" s="41"/>
       <c r="E331" s="40"/>
       <c r="F331" s="35"/>
@@ -9995,11 +10044,10 @@
       <c r="H331" s="40"/>
       <c r="I331" s="36"/>
       <c r="L331" s="46"/>
-      <c r="M331" s="117"/>
     </row>
     <row r="332" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B332" s="39"/>
-      <c r="C332" s="40"/>
+      <c r="C332" s="39"/>
       <c r="D332" s="41"/>
       <c r="E332" s="40"/>
       <c r="F332" s="35"/>
@@ -10071,38 +10119,38 @@
     </row>
     <row r="338" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B338" s="39"/>
-      <c r="C338" s="35"/>
-      <c r="D338" s="37"/>
+      <c r="C338" s="40"/>
+      <c r="D338" s="41"/>
       <c r="E338" s="40"/>
       <c r="F338" s="35"/>
       <c r="G338" s="52"/>
-      <c r="H338" s="35"/>
+      <c r="H338" s="40"/>
       <c r="I338" s="36"/>
       <c r="L338" s="46"/>
-      <c r="M338" s="119"/>
+      <c r="M338" s="117"/>
     </row>
     <row r="339" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B339" s="39"/>
-      <c r="C339" s="40"/>
+      <c r="C339" s="35"/>
       <c r="D339" s="37"/>
-      <c r="E339" s="35"/>
+      <c r="E339" s="40"/>
       <c r="F339" s="35"/>
       <c r="G339" s="52"/>
       <c r="H339" s="35"/>
       <c r="I339" s="36"/>
       <c r="L339" s="46"/>
+      <c r="M339" s="119"/>
     </row>
     <row r="340" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B340" s="39"/>
       <c r="C340" s="40"/>
-      <c r="D340" s="41"/>
-      <c r="E340" s="40"/>
+      <c r="D340" s="37"/>
+      <c r="E340" s="35"/>
       <c r="F340" s="35"/>
       <c r="G340" s="52"/>
-      <c r="H340" s="40"/>
+      <c r="H340" s="35"/>
       <c r="I340" s="36"/>
       <c r="L340" s="46"/>
-      <c r="M340" s="117"/>
     </row>
     <row r="341" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B341" s="39"/>
@@ -10150,6 +10198,7 @@
       <c r="H344" s="40"/>
       <c r="I344" s="36"/>
       <c r="L344" s="46"/>
+      <c r="M344" s="117"/>
     </row>
     <row r="345" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B345" s="39"/>
@@ -10161,7 +10210,6 @@
       <c r="H345" s="40"/>
       <c r="I345" s="36"/>
       <c r="L345" s="46"/>
-      <c r="M345" s="117"/>
     </row>
     <row r="346" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B346" s="39"/>
@@ -10190,9 +10238,9 @@
     <row r="348" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B348" s="39"/>
       <c r="C348" s="40"/>
-      <c r="D348" s="40"/>
+      <c r="D348" s="41"/>
       <c r="E348" s="40"/>
-      <c r="F348" s="40"/>
+      <c r="F348" s="35"/>
       <c r="G348" s="52"/>
       <c r="H348" s="40"/>
       <c r="I348" s="36"/>
@@ -10245,6 +10293,7 @@
       <c r="H352" s="40"/>
       <c r="I352" s="36"/>
       <c r="L352" s="46"/>
+      <c r="M352" s="117"/>
     </row>
     <row r="353" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B353" s="39"/>
@@ -10270,26 +10319,26 @@
     </row>
     <row r="355" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B355" s="39"/>
-      <c r="C355" s="35"/>
-      <c r="D355" s="35"/>
-      <c r="E355" s="35"/>
-      <c r="F355" s="35"/>
+      <c r="C355" s="40"/>
+      <c r="D355" s="40"/>
+      <c r="E355" s="40"/>
+      <c r="F355" s="40"/>
       <c r="G355" s="52"/>
-      <c r="H355" s="35"/>
+      <c r="H355" s="40"/>
       <c r="I355" s="36"/>
       <c r="L355" s="46"/>
-      <c r="M355" s="118"/>
     </row>
     <row r="356" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B356" s="39"/>
-      <c r="C356" s="40"/>
-      <c r="D356" s="40"/>
-      <c r="E356" s="40"/>
-      <c r="F356" s="40"/>
+      <c r="C356" s="35"/>
+      <c r="D356" s="35"/>
+      <c r="E356" s="35"/>
+      <c r="F356" s="35"/>
       <c r="G356" s="52"/>
-      <c r="H356" s="40"/>
+      <c r="H356" s="35"/>
       <c r="I356" s="36"/>
       <c r="L356" s="46"/>
+      <c r="M356" s="118"/>
     </row>
     <row r="357" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B357" s="39"/>
@@ -10411,31 +10460,30 @@
       <c r="H367" s="40"/>
       <c r="I367" s="36"/>
       <c r="L367" s="46"/>
-      <c r="M367" s="117"/>
     </row>
     <row r="368" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B368" s="39"/>
-      <c r="C368" s="35"/>
-      <c r="D368" s="35"/>
-      <c r="E368" s="35"/>
-      <c r="F368" s="35"/>
+      <c r="C368" s="40"/>
+      <c r="D368" s="40"/>
+      <c r="E368" s="40"/>
+      <c r="F368" s="40"/>
       <c r="G368" s="52"/>
-      <c r="H368" s="35"/>
+      <c r="H368" s="40"/>
       <c r="I368" s="36"/>
       <c r="L368" s="46"/>
-      <c r="M368" s="118"/>
+      <c r="M368" s="117"/>
     </row>
     <row r="369" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B369" s="39"/>
-      <c r="C369" s="40"/>
-      <c r="D369" s="40"/>
-      <c r="E369" s="40"/>
-      <c r="F369" s="40"/>
+      <c r="C369" s="35"/>
+      <c r="D369" s="35"/>
+      <c r="E369" s="35"/>
+      <c r="F369" s="35"/>
       <c r="G369" s="52"/>
-      <c r="H369" s="40"/>
+      <c r="H369" s="35"/>
       <c r="I369" s="36"/>
       <c r="L369" s="46"/>
-      <c r="M369" s="117"/>
+      <c r="M369" s="118"/>
     </row>
     <row r="370" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B370" s="39"/>
@@ -10453,40 +10501,41 @@
       <c r="B371" s="39"/>
       <c r="C371" s="40"/>
       <c r="D371" s="40"/>
-      <c r="E371" s="48"/>
-      <c r="F371" s="48"/>
+      <c r="E371" s="40"/>
+      <c r="F371" s="40"/>
       <c r="G371" s="52"/>
       <c r="H371" s="40"/>
       <c r="I371" s="36"/>
       <c r="L371" s="46"/>
+      <c r="M371" s="117"/>
     </row>
     <row r="372" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B372" s="39"/>
-      <c r="C372" s="35"/>
-      <c r="D372" s="35"/>
-      <c r="E372" s="35"/>
-      <c r="F372" s="35"/>
+      <c r="C372" s="40"/>
+      <c r="D372" s="40"/>
+      <c r="E372" s="48"/>
+      <c r="F372" s="48"/>
       <c r="G372" s="52"/>
-      <c r="H372" s="35"/>
+      <c r="H372" s="40"/>
       <c r="I372" s="36"/>
       <c r="L372" s="46"/>
-      <c r="M372" s="118"/>
     </row>
     <row r="373" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B373" s="39"/>
-      <c r="C373" s="40"/>
-      <c r="D373" s="40"/>
-      <c r="E373" s="40"/>
-      <c r="F373" s="40"/>
+      <c r="C373" s="35"/>
+      <c r="D373" s="35"/>
+      <c r="E373" s="35"/>
+      <c r="F373" s="35"/>
       <c r="G373" s="52"/>
-      <c r="H373" s="40"/>
+      <c r="H373" s="35"/>
       <c r="I373" s="36"/>
       <c r="L373" s="46"/>
+      <c r="M373" s="118"/>
     </row>
     <row r="374" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B374" s="39"/>
       <c r="C374" s="40"/>
-      <c r="D374" s="49"/>
+      <c r="D374" s="40"/>
       <c r="E374" s="40"/>
       <c r="F374" s="40"/>
       <c r="G374" s="52"/>
@@ -10496,10 +10545,10 @@
     </row>
     <row r="375" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B375" s="39"/>
-      <c r="C375" s="48"/>
-      <c r="D375" s="40"/>
-      <c r="E375" s="48"/>
-      <c r="F375" s="48"/>
+      <c r="C375" s="40"/>
+      <c r="D375" s="49"/>
+      <c r="E375" s="40"/>
+      <c r="F375" s="40"/>
       <c r="G375" s="52"/>
       <c r="H375" s="40"/>
       <c r="I375" s="36"/>
@@ -10507,10 +10556,10 @@
     </row>
     <row r="376" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B376" s="39"/>
-      <c r="C376" s="40"/>
+      <c r="C376" s="48"/>
       <c r="D376" s="40"/>
-      <c r="E376" s="40"/>
-      <c r="F376" s="40"/>
+      <c r="E376" s="48"/>
+      <c r="F376" s="48"/>
       <c r="G376" s="52"/>
       <c r="H376" s="40"/>
       <c r="I376" s="36"/>
@@ -10595,23 +10644,23 @@
     </row>
     <row r="384" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B384" s="39"/>
-      <c r="C384" s="48"/>
+      <c r="C384" s="40"/>
       <c r="D384" s="40"/>
       <c r="E384" s="40"/>
       <c r="F384" s="40"/>
       <c r="G384" s="52"/>
-      <c r="H384" s="50"/>
+      <c r="H384" s="40"/>
       <c r="I384" s="36"/>
       <c r="L384" s="46"/>
     </row>
     <row r="385" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B385" s="39"/>
-      <c r="C385" s="40"/>
+      <c r="C385" s="48"/>
       <c r="D385" s="40"/>
       <c r="E385" s="40"/>
       <c r="F385" s="40"/>
       <c r="G385" s="52"/>
-      <c r="H385" s="40"/>
+      <c r="H385" s="50"/>
       <c r="I385" s="36"/>
       <c r="L385" s="46"/>
     </row>
@@ -10647,7 +10696,6 @@
       <c r="H388" s="40"/>
       <c r="I388" s="36"/>
       <c r="L388" s="46"/>
-      <c r="M388" s="117"/>
     </row>
     <row r="389" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B389" s="39"/>
@@ -10659,19 +10707,19 @@
       <c r="H389" s="40"/>
       <c r="I389" s="36"/>
       <c r="L389" s="46"/>
-      <c r="M389" s="120"/>
+      <c r="M389" s="117"/>
     </row>
     <row r="390" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B390" s="39"/>
-      <c r="C390" s="35"/>
-      <c r="D390" s="35"/>
-      <c r="E390" s="35"/>
-      <c r="F390" s="35"/>
+      <c r="C390" s="40"/>
+      <c r="D390" s="40"/>
+      <c r="E390" s="40"/>
+      <c r="F390" s="40"/>
       <c r="G390" s="52"/>
-      <c r="H390" s="35"/>
+      <c r="H390" s="40"/>
       <c r="I390" s="36"/>
       <c r="L390" s="46"/>
-      <c r="M390" s="118"/>
+      <c r="M390" s="120"/>
     </row>
     <row r="391" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B391" s="39"/>
@@ -10687,15 +10735,15 @@
     </row>
     <row r="392" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B392" s="39"/>
-      <c r="C392" s="40"/>
-      <c r="D392" s="40"/>
-      <c r="E392" s="40"/>
-      <c r="F392" s="40"/>
+      <c r="C392" s="35"/>
+      <c r="D392" s="35"/>
+      <c r="E392" s="35"/>
+      <c r="F392" s="35"/>
       <c r="G392" s="52"/>
-      <c r="H392" s="40"/>
+      <c r="H392" s="35"/>
       <c r="I392" s="36"/>
       <c r="L392" s="46"/>
-      <c r="M392" s="117"/>
+      <c r="M392" s="118"/>
     </row>
     <row r="393" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B393" s="39"/>
@@ -10704,34 +10752,34 @@
       <c r="E393" s="40"/>
       <c r="F393" s="40"/>
       <c r="G393" s="52"/>
-      <c r="H393" s="35"/>
+      <c r="H393" s="40"/>
       <c r="I393" s="36"/>
       <c r="L393" s="46"/>
       <c r="M393" s="117"/>
     </row>
     <row r="394" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B394" s="39"/>
-      <c r="C394" s="35"/>
-      <c r="D394" s="35"/>
-      <c r="E394" s="35"/>
-      <c r="F394" s="35"/>
+      <c r="C394" s="40"/>
+      <c r="D394" s="40"/>
+      <c r="E394" s="40"/>
+      <c r="F394" s="40"/>
       <c r="G394" s="52"/>
       <c r="H394" s="35"/>
       <c r="I394" s="36"/>
       <c r="L394" s="46"/>
-      <c r="M394" s="118"/>
+      <c r="M394" s="117"/>
     </row>
     <row r="395" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B395" s="39"/>
-      <c r="C395" s="40"/>
-      <c r="D395" s="40"/>
-      <c r="E395" s="40"/>
-      <c r="F395" s="40"/>
+      <c r="C395" s="35"/>
+      <c r="D395" s="35"/>
+      <c r="E395" s="35"/>
+      <c r="F395" s="35"/>
       <c r="G395" s="52"/>
-      <c r="H395" s="40"/>
+      <c r="H395" s="35"/>
       <c r="I395" s="36"/>
       <c r="L395" s="46"/>
-      <c r="M395" s="117"/>
+      <c r="M395" s="118"/>
     </row>
     <row r="396" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B396" s="39"/>
@@ -10977,19 +11025,20 @@
       <c r="B416" s="39"/>
       <c r="C416" s="40"/>
       <c r="D416" s="40"/>
-      <c r="E416" s="35"/>
-      <c r="F416" s="35"/>
+      <c r="E416" s="40"/>
+      <c r="F416" s="40"/>
       <c r="G416" s="52"/>
       <c r="H416" s="40"/>
       <c r="I416" s="36"/>
       <c r="L416" s="46"/>
+      <c r="M416" s="117"/>
     </row>
     <row r="417" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B417" s="39"/>
       <c r="C417" s="40"/>
       <c r="D417" s="40"/>
-      <c r="E417" s="40"/>
-      <c r="F417" s="40"/>
+      <c r="E417" s="35"/>
+      <c r="F417" s="35"/>
       <c r="G417" s="52"/>
       <c r="H417" s="40"/>
       <c r="I417" s="36"/>
@@ -11005,7 +11054,6 @@
       <c r="H418" s="40"/>
       <c r="I418" s="36"/>
       <c r="L418" s="46"/>
-      <c r="M418" s="117"/>
     </row>
     <row r="419" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B419" s="39"/>
@@ -11021,7 +11069,7 @@
     </row>
     <row r="420" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B420" s="39"/>
-      <c r="C420" s="48"/>
+      <c r="C420" s="40"/>
       <c r="D420" s="40"/>
       <c r="E420" s="40"/>
       <c r="F420" s="40"/>
@@ -11033,10 +11081,11 @@
     </row>
     <row r="421" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B421" s="39"/>
-      <c r="C421" s="40"/>
+      <c r="C421" s="48"/>
       <c r="D421" s="40"/>
       <c r="E421" s="40"/>
       <c r="F421" s="40"/>
+      <c r="G421" s="52"/>
       <c r="H421" s="40"/>
       <c r="I421" s="36"/>
       <c r="L421" s="46"/>
@@ -11106,6 +11155,7 @@
       <c r="H427" s="40"/>
       <c r="I427" s="36"/>
       <c r="L427" s="46"/>
+      <c r="M427" s="117"/>
     </row>
     <row r="428" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B428" s="39"/>
@@ -11201,8 +11251,8 @@
       <c r="B437" s="39"/>
       <c r="C437" s="40"/>
       <c r="D437" s="40"/>
-      <c r="E437" s="39"/>
-      <c r="F437" s="39"/>
+      <c r="E437" s="40"/>
+      <c r="F437" s="40"/>
       <c r="H437" s="40"/>
       <c r="I437" s="36"/>
       <c r="L437" s="46"/>
@@ -11211,8 +11261,8 @@
       <c r="B438" s="39"/>
       <c r="C438" s="40"/>
       <c r="D438" s="40"/>
-      <c r="E438" s="40"/>
-      <c r="F438" s="40"/>
+      <c r="E438" s="39"/>
+      <c r="F438" s="39"/>
       <c r="H438" s="40"/>
       <c r="I438" s="36"/>
       <c r="L438" s="46"/>
@@ -11226,7 +11276,6 @@
       <c r="H439" s="40"/>
       <c r="I439" s="36"/>
       <c r="L439" s="46"/>
-      <c r="M439" s="117"/>
     </row>
     <row r="440" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B440" s="39"/>
@@ -11272,15 +11321,26 @@
       <c r="L443" s="46"/>
       <c r="M443" s="117"/>
     </row>
+    <row r="444" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B444" s="39"/>
+      <c r="C444" s="40"/>
+      <c r="D444" s="40"/>
+      <c r="E444" s="40"/>
+      <c r="F444" s="40"/>
+      <c r="H444" s="40"/>
+      <c r="I444" s="36"/>
+      <c r="L444" s="46"/>
+      <c r="M444" s="117"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B247:B298 B300:B333 B131:B136 B338:B443" xr:uid="{8C405A5E-7043-445E-843A-77F75AAA649B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="B248:B299 B301:B334 B132:B137 B339:B444" xr:uid="{8C405A5E-7043-445E-843A-77F75AAA649B}">
       <formula1>"Critical Error,Error,Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B299 B137:B246 B302 B334:B337" xr:uid="{EA50A853-E1EC-4CC3-AC83-044F98363F81}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B300 B138:B247 B303 B335:B338" xr:uid="{EA50A853-E1EC-4CC3-AC83-044F98363F81}">
       <formula1>"Critical Error, Error, Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B130" xr:uid="{4888DB0A-C02B-4EB3-BB1F-600FE505C129}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B131" xr:uid="{4888DB0A-C02B-4EB3-BB1F-600FE505C129}">
       <formula1>"C,E,W"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11297,7 +11357,7 @@
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
     <col min="3" max="3" width="45.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11319,7 +11379,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="C2" t="s">
         <v>547</v>
@@ -11330,13 +11390,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>552</v>
+        <v>587</v>
       </c>
       <c r="C3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D3" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11344,13 +11404,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>553</v>
+        <v>588</v>
       </c>
       <c r="C4" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D4" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11358,13 +11418,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="C5" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D5" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11372,19 +11432,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="C6" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="128" t="s">
-        <v>559</v>
-      </c>
-      <c r="B8" s="128"/>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
+      <c r="A8" s="127" t="s">
+        <v>552</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11458,7 +11518,7 @@
         <v>251</v>
       </c>
       <c r="B3" s="106">
-        <v>46236</v>
+        <v>46303</v>
       </c>
       <c r="C3" t="s">
         <v>189</v>
@@ -11467,7 +11527,7 @@
         <v>2001</v>
       </c>
       <c r="E3" s="80">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H3" s="58" t="s">
         <v>195</v>
